--- a/ADET/teams and titles of adet.xlsx
+++ b/ADET/teams and titles of adet.xlsx
@@ -728,7 +728,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -736,11 +736,26 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -763,11 +778,14 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3191,827 +3209,911 @@
   <cols>
     <col min="1" max="1" style="4" width="9.140625"/>
     <col customWidth="1" min="2" max="2" width="35.7109375"/>
-    <col customWidth="1" min="3" max="3" style="1" width="39.28125"/>
+    <col customWidth="1" min="3" max="3" style="1" width="8.421875"/>
     <col customWidth="1" min="4" max="4" style="3" width="46.421875"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="11" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="4">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="4"/>
-      <c r="B3" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="3"/>
+      <c r="C3" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="4"/>
-      <c r="B4" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="3"/>
+      <c r="C4" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="4"/>
-      <c r="B5" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="3"/>
+      <c r="C5" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="11"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="4">
+      <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="4"/>
-      <c r="B7" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="3"/>
+      <c r="C7" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="11"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="4"/>
-      <c r="B8" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="3"/>
+      <c r="C8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="4"/>
-      <c r="B9" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="3"/>
+      <c r="C9" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="11"/>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="4">
+      <c r="A10" s="8">
         <v>3</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="4"/>
-      <c r="B11" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="3"/>
+      <c r="C11" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="11"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="3"/>
+      <c r="C12" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="11"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="4"/>
-      <c r="B13" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="3"/>
+      <c r="C13" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="11"/>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="4">
+      <c r="A14" s="8">
         <v>4</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="4"/>
-      <c r="B15" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="3"/>
+      <c r="C15" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="11"/>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="4"/>
-      <c r="B16" t="s">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="3"/>
+      <c r="C16" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="11"/>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="4"/>
-      <c r="B17" t="s">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D17" s="3"/>
+      <c r="C17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="11"/>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="4">
+      <c r="A18" s="8">
         <v>5</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="4"/>
-      <c r="B19" t="s">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D19" s="3"/>
+      <c r="C19" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="11"/>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="4"/>
-      <c r="B20" t="s">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D20" s="3"/>
+      <c r="C20" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="11"/>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="4"/>
-      <c r="B21" t="s">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="3"/>
+      <c r="C21" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="4">
+      <c r="A22" s="8">
         <v>6</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C22" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="4"/>
-      <c r="B23" t="s">
+      <c r="A23" s="8"/>
+      <c r="B23" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D23" s="3"/>
+      <c r="C23" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="4"/>
-      <c r="B24" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="3"/>
+      <c r="C24" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="4"/>
-      <c r="B25" t="s">
+      <c r="A25" s="8"/>
+      <c r="B25" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="3"/>
+      <c r="C25" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="11"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="4">
+      <c r="A26" s="8">
         <v>7</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="C26" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="4"/>
-      <c r="B27" t="s">
+      <c r="A27" s="8"/>
+      <c r="B27" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" s="3"/>
+      <c r="C27" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="11"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="4"/>
-      <c r="B28" t="s">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="3"/>
+      <c r="C28" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="4"/>
-      <c r="B29" t="s">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="3"/>
+      <c r="C29" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="11"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="4">
+      <c r="A30" s="8">
         <v>8</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="C30" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="4"/>
-      <c r="B31" t="s">
+      <c r="A31" s="8"/>
+      <c r="B31" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="3"/>
+      <c r="C31" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="11"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="4"/>
-      <c r="B32" t="s">
+      <c r="A32" s="8"/>
+      <c r="B32" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" s="3"/>
+      <c r="C32" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="11"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="4"/>
-      <c r="B33" t="s">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="3"/>
+      <c r="C33" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33" s="11"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="4">
+      <c r="A34" s="8">
         <v>9</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="C34" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="4"/>
-      <c r="B35" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" s="3"/>
+      <c r="C35" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="11"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="4"/>
-      <c r="B36" t="s">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" s="3"/>
+      <c r="C36" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="11"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="4"/>
-      <c r="B37" t="s">
+      <c r="A37" s="8"/>
+      <c r="B37" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" s="3"/>
+      <c r="C37" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" s="11"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="4">
+      <c r="A38" s="8">
         <v>10</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="C38" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="4"/>
-      <c r="B39" t="s">
+      <c r="A39" s="8"/>
+      <c r="B39" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="3"/>
+      <c r="C39" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="11"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="4"/>
-      <c r="B40" t="s">
+      <c r="A40" s="8"/>
+      <c r="B40" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="3"/>
+      <c r="C40" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="11"/>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="4"/>
-      <c r="B41" t="s">
+      <c r="A41" s="8"/>
+      <c r="B41" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D41" s="3"/>
+      <c r="C41" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" s="11"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="4">
+      <c r="A42" s="8">
         <v>11</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="3" t="s">
+      <c r="C42" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="4"/>
-      <c r="B43" t="s">
+      <c r="A43" s="8"/>
+      <c r="B43" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D43" s="3"/>
+      <c r="C43" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="11"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="4"/>
-      <c r="B44" t="s">
+      <c r="A44" s="8"/>
+      <c r="B44" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="3"/>
+      <c r="C44" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="11"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="4"/>
-      <c r="B45" t="s">
+      <c r="A45" s="8"/>
+      <c r="B45" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="3"/>
+      <c r="C45" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" s="11"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="4">
+      <c r="A46" s="8">
         <v>12</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="3" t="s">
+      <c r="C46" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="4"/>
-      <c r="B47" t="s">
+      <c r="A47" s="8"/>
+      <c r="B47" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="3"/>
+      <c r="C47" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="11"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="4"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="3"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="4"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="3"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="11"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="4">
+      <c r="A50" s="8">
         <v>13</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="C50" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="4"/>
-      <c r="B51" t="s">
+      <c r="A51" s="8"/>
+      <c r="B51" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D51" s="3"/>
+      <c r="C51" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" s="11"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="4"/>
-      <c r="B52" t="s">
+      <c r="A52" s="8"/>
+      <c r="B52" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D52" s="3"/>
+      <c r="C52" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="11"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="4"/>
-      <c r="B53" t="s">
+      <c r="A53" s="8"/>
+      <c r="B53" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53" s="3"/>
+      <c r="C53" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="11"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="4">
+      <c r="A54" s="8">
         <v>14</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" s="3" t="s">
+      <c r="C54" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="4"/>
-      <c r="B55" t="s">
+      <c r="A55" s="8"/>
+      <c r="B55" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D55" s="3"/>
+      <c r="C55" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" s="11"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="4"/>
-      <c r="B56" t="s">
+      <c r="A56" s="8"/>
+      <c r="B56" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" s="3"/>
+      <c r="C56" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D56" s="11"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="4"/>
-      <c r="D57" s="3"/>
+      <c r="A57" s="8"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="11"/>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="4">
+      <c r="A58" s="8">
         <v>15</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D58" s="10" t="s">
+      <c r="C58" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="4"/>
-      <c r="B59" t="s">
+      <c r="A59" s="8"/>
+      <c r="B59" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="3"/>
+      <c r="C59" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" s="11"/>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="4"/>
-      <c r="B60" t="s">
+      <c r="A60" s="8"/>
+      <c r="B60" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="3"/>
+      <c r="C60" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" s="11"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="4"/>
-      <c r="B61" t="s">
+      <c r="A61" s="8"/>
+      <c r="B61" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D61" s="3"/>
+      <c r="C61" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D61" s="11"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="4"/>
-      <c r="D62" s="3"/>
+      <c r="A62" s="8"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="11"/>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="4"/>
-      <c r="D63" s="3"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="11"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="4"/>
-      <c r="D64" s="3"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="4"/>
-      <c r="D65" s="3"/>
+      <c r="A65" s="8"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="11"/>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="4"/>
-      <c r="D66" s="3"/>
+      <c r="A66" s="8"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="11"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="4"/>
-      <c r="D67" s="3"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="11"/>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="4"/>
-      <c r="D68" s="3"/>
+      <c r="A68" s="8"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="11"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="4"/>
-      <c r="D69" s="3"/>
+      <c r="A69" s="8"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="11"/>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="4"/>
-      <c r="D70" s="3"/>
+      <c r="A70" s="8"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="11"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="4"/>
-      <c r="D71" s="3"/>
+      <c r="A71" s="8"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="11"/>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="4"/>
-      <c r="D72" s="3"/>
+      <c r="A72" s="8"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="4"/>
-      <c r="D73" s="3"/>
+      <c r="A73" s="8"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="11"/>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="4"/>
-      <c r="D74" s="3"/>
+      <c r="A74" s="8"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="11"/>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="4"/>
-      <c r="D75" s="3"/>
+      <c r="A75" s="8"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="11"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="4"/>
-      <c r="D76" s="3"/>
+      <c r="A76" s="8"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="4"/>
-      <c r="D77" s="3"/>
+      <c r="A77" s="8"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="11"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="4"/>
-      <c r="D78" s="3"/>
+      <c r="A78" s="8"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="11"/>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="4"/>
-      <c r="D79" s="3"/>
+      <c r="A79" s="8"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="11"/>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="4"/>
-      <c r="D80" s="3"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="11"/>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="4"/>
-      <c r="D81" s="3"/>
+      <c r="A81" s="8"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="11"/>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="4"/>
-      <c r="D82" s="3"/>
+      <c r="A82" s="8"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="11"/>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="4"/>
-      <c r="D83" s="3"/>
+      <c r="A83" s="8"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="11"/>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="4"/>
-      <c r="D84" s="3"/>
+      <c r="A84" s="8"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85" s="4"/>
-      <c r="D85" s="3"/>
+      <c r="A85" s="8"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="11"/>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86" s="4"/>
-      <c r="D86" s="3"/>
+      <c r="A86" s="8"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="11"/>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87" s="4"/>
-      <c r="D87" s="3"/>
+      <c r="A87" s="8"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="11"/>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88" s="4"/>
-      <c r="D88" s="3"/>
+      <c r="A88" s="8"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89" s="4"/>
-      <c r="D89" s="3"/>
+      <c r="A89" s="8"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="10"/>
+      <c r="D89" s="11"/>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90" s="4"/>
-      <c r="D90" s="3"/>
+      <c r="A90" s="8"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="11"/>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91" s="4"/>
-      <c r="D91" s="3"/>
+      <c r="A91" s="8"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="11"/>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92" s="4"/>
-      <c r="D92" s="3"/>
+      <c r="A92" s="8"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="11"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="A93" s="4"/>
-      <c r="D93" s="3"/>
+      <c r="A93" s="8"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="11"/>
     </row>
     <row r="94" ht="14.25">
-      <c r="A94" s="4"/>
-      <c r="D94" s="3"/>
+      <c r="A94" s="8"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="11"/>
     </row>
     <row r="95" ht="14.25">
-      <c r="A95" s="4"/>
-      <c r="D95" s="3"/>
+      <c r="A95" s="8"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="11"/>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96" s="4"/>
-      <c r="D96" s="3"/>
+      <c r="A96" s="8"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97" s="4"/>
-      <c r="D97" s="3"/>
+      <c r="A97" s="8"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="11"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="A98" s="4"/>
-      <c r="D98" s="3"/>
+      <c r="A98" s="8"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="11"/>
     </row>
     <row r="99" ht="14.25">
-      <c r="A99" s="4"/>
-      <c r="D99" s="3"/>
+      <c r="A99" s="8"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="11"/>
     </row>
     <row r="100" ht="14.25">
-      <c r="A100" s="4"/>
-      <c r="D100" s="3"/>
+      <c r="A100" s="8"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
     </row>
     <row r="101" ht="14.25">
-      <c r="A101" s="4"/>
-      <c r="D101" s="3"/>
+      <c r="A101" s="8"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="10"/>
+      <c r="D101" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="50">
@@ -4066,9 +4168,9 @@
     <mergeCell ref="A98:A101"/>
     <mergeCell ref="D98:D101"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/ADET/teams and titles of adet.xlsx
+++ b/ADET/teams and titles of adet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="3g" sheetId="1" state="visible" r:id="rId2"/>
@@ -755,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -772,21 +772,24 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1">
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2417,729 +2420,729 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.140625"/>
-    <col customWidth="1" min="2" max="2" width="22.7109375"/>
-    <col customWidth="1" min="3" max="3" style="6" width="18.421875"/>
-    <col customWidth="1" min="4" max="4" style="4" width="63.28125"/>
+    <col min="1" max="1" style="6" width="9.140625"/>
+    <col customWidth="1" min="2" max="2" style="7" width="22.7109375"/>
+    <col customWidth="1" min="3" max="3" style="8" width="8.8515625"/>
+    <col customWidth="1" min="4" max="4" style="9" width="63.28125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4"/>
-      <c r="B3" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="3"/>
+      <c r="C3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="3"/>
+      <c r="C4" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="10"/>
     </row>
     <row r="5">
-      <c r="A5" s="4"/>
-      <c r="B5" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="3"/>
+      <c r="C5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="4">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="3"/>
+      <c r="C7" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="3"/>
+      <c r="C8" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="4">
+      <c r="A9" s="9">
         <v>3</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="3"/>
+      <c r="C10" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="10"/>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="7" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="3"/>
+      <c r="C11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="10"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="4">
+      <c r="A12" s="9">
         <v>4</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="4"/>
-      <c r="B13" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="4"/>
+      <c r="C13" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="4"/>
-      <c r="B14" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" s="4"/>
+      <c r="C14" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="4"/>
-      <c r="B15" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="4"/>
+      <c r="C15" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="9"/>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="4">
+      <c r="A16" s="9">
         <v>5</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="4"/>
-      <c r="B17" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="5"/>
+      <c r="C17" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="4"/>
-      <c r="B18" t="s">
+      <c r="A18" s="9"/>
+      <c r="B18" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="5"/>
+      <c r="C18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="4"/>
-      <c r="B19" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="5"/>
+      <c r="C19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="4">
+      <c r="A20" s="9">
         <v>6</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="C20" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="4"/>
-      <c r="B21" t="s">
+      <c r="A21" s="9"/>
+      <c r="B21" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="4"/>
+      <c r="C21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="9"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="4"/>
-      <c r="B22" t="s">
+      <c r="A22" s="9"/>
+      <c r="B22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="4"/>
+      <c r="C22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="9"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="A23" s="9"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="4">
+      <c r="A24" s="9">
         <v>7</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="C24" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="4"/>
-      <c r="B25" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="5"/>
+      <c r="C25" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="4"/>
-      <c r="B26" t="s">
+      <c r="A26" s="9"/>
+      <c r="B26" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="5"/>
+      <c r="C26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="12"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="4"/>
-      <c r="B27" t="s">
+      <c r="A27" s="9"/>
+      <c r="B27" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="5"/>
+      <c r="C27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="12"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="4">
+      <c r="A28" s="9">
         <v>8</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="C28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="4"/>
-      <c r="B29" t="s">
+      <c r="A29" s="9"/>
+      <c r="B29" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="4"/>
+      <c r="C29" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="9"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="4"/>
-      <c r="B30" t="s">
+      <c r="A30" s="9"/>
+      <c r="B30" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="4"/>
+      <c r="C30" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="4"/>
-      <c r="B31" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="4"/>
+      <c r="C31" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="9"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="4">
+      <c r="A32" s="9">
         <v>9</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="C32" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="4"/>
-      <c r="B33" t="s">
+      <c r="A33" s="9"/>
+      <c r="B33" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" s="4"/>
+      <c r="C33" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="9"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="4"/>
-      <c r="B34" t="s">
+      <c r="A34" s="9"/>
+      <c r="B34" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" s="4"/>
+      <c r="C34" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="9"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="4"/>
-      <c r="B35" t="s">
+      <c r="A35" s="9"/>
+      <c r="B35" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" s="4"/>
+      <c r="C35" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="9"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="4">
+      <c r="A36" s="9">
         <v>10</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="C36" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="4"/>
-      <c r="B37" t="s">
+      <c r="A37" s="9"/>
+      <c r="B37" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" s="3"/>
+      <c r="C37" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" s="10"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="4"/>
-      <c r="B38" t="s">
+      <c r="A38" s="9"/>
+      <c r="B38" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38" s="3"/>
+      <c r="C38" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="10"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="4"/>
-      <c r="D39" s="3"/>
+      <c r="A39" s="9"/>
+      <c r="D39" s="10"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="4">
+      <c r="A40" s="9">
         <v>11</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="C40" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="4"/>
-      <c r="B41" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" s="4"/>
+      <c r="C41" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="9"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="4"/>
-      <c r="B42" t="s">
+      <c r="A42" s="9"/>
+      <c r="B42" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42" s="4"/>
+      <c r="C42" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="9"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="4"/>
-      <c r="B43" t="s">
+      <c r="A43" s="9"/>
+      <c r="B43" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43" s="4"/>
+      <c r="C43" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="9"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44"/>
-      <c r="B44" t="s">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D44"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45"/>
-      <c r="B45" t="s">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D45"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46"/>
-      <c r="B46" t="s">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D46"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47"/>
-      <c r="B47" t="s">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D47"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48"/>
-      <c r="D48"/>
+      <c r="A48" s="7"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49"/>
-      <c r="D49"/>
+      <c r="A49" s="7"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50"/>
-      <c r="D50"/>
+      <c r="A50" s="7"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51"/>
-      <c r="D51"/>
+      <c r="A51" s="7"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52"/>
-      <c r="D52"/>
+      <c r="A52" s="7"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53"/>
-      <c r="D53"/>
+      <c r="A53" s="7"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54"/>
-      <c r="D54"/>
+      <c r="A54" s="7"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55"/>
-      <c r="D55"/>
+      <c r="A55" s="7"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56"/>
-      <c r="D56"/>
+      <c r="A56" s="7"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57"/>
-      <c r="D57"/>
+      <c r="A57" s="7"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58"/>
-      <c r="D58"/>
+      <c r="A58" s="7"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59"/>
-      <c r="D59"/>
+      <c r="A59" s="7"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60"/>
-      <c r="D60"/>
+      <c r="A60" s="7"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61"/>
-      <c r="D61"/>
+      <c r="A61" s="7"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62"/>
-      <c r="D62"/>
+      <c r="A62" s="7"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63"/>
-      <c r="D63"/>
+      <c r="A63" s="7"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64"/>
-      <c r="D64"/>
+      <c r="A64" s="7"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65"/>
-      <c r="D65"/>
+      <c r="A65" s="7"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66"/>
-      <c r="D66"/>
+      <c r="A66" s="7"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67"/>
-      <c r="D67"/>
+      <c r="A67" s="7"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68"/>
-      <c r="D68"/>
+      <c r="A68" s="7"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69"/>
-      <c r="D69"/>
+      <c r="A69" s="7"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70"/>
-      <c r="D70"/>
+      <c r="A70" s="7"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71"/>
-      <c r="D71"/>
+      <c r="A71" s="7"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72"/>
-      <c r="D72"/>
+      <c r="A72" s="7"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73"/>
-      <c r="D73"/>
+      <c r="A73" s="7"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74"/>
-      <c r="D74"/>
+      <c r="A74" s="7"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75"/>
-      <c r="D75"/>
+      <c r="A75" s="7"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76"/>
-      <c r="D76"/>
+      <c r="A76" s="7"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77"/>
-      <c r="D77"/>
+      <c r="A77" s="7"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78"/>
-      <c r="D78"/>
+      <c r="A78" s="7"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79"/>
-      <c r="D79"/>
+      <c r="A79" s="7"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80"/>
-      <c r="D80"/>
+      <c r="A80" s="7"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81"/>
-      <c r="D81"/>
+      <c r="A81" s="7"/>
+      <c r="D81" s="7"/>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82"/>
-      <c r="D82"/>
+      <c r="A82" s="7"/>
+      <c r="D82" s="7"/>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83"/>
-      <c r="D83"/>
+      <c r="A83" s="7"/>
+      <c r="D83" s="7"/>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84"/>
-      <c r="D84"/>
+      <c r="A84" s="7"/>
+      <c r="D84" s="7"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85"/>
-      <c r="D85"/>
+      <c r="A85" s="7"/>
+      <c r="D85" s="7"/>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86"/>
-      <c r="D86"/>
+      <c r="A86" s="7"/>
+      <c r="D86" s="7"/>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87"/>
-      <c r="D87"/>
+      <c r="A87" s="7"/>
+      <c r="D87" s="7"/>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88"/>
-      <c r="D88"/>
+      <c r="A88" s="7"/>
+      <c r="D88" s="7"/>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89"/>
-      <c r="D89"/>
+      <c r="A89" s="7"/>
+      <c r="D89" s="7"/>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90"/>
-      <c r="D90"/>
+      <c r="A90" s="7"/>
+      <c r="D90" s="7"/>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91"/>
-      <c r="D91"/>
+      <c r="A91" s="7"/>
+      <c r="D91" s="7"/>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92"/>
-      <c r="D92"/>
+      <c r="A92" s="7"/>
+      <c r="D92" s="7"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="A93"/>
-      <c r="D93"/>
+      <c r="A93" s="7"/>
+      <c r="D93" s="7"/>
     </row>
     <row r="94" ht="14.25">
-      <c r="A94"/>
-      <c r="D94"/>
+      <c r="A94" s="7"/>
+      <c r="D94" s="7"/>
     </row>
     <row r="95" ht="14.25">
-      <c r="A95"/>
-      <c r="D95"/>
+      <c r="A95" s="7"/>
+      <c r="D95" s="7"/>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96"/>
-      <c r="D96"/>
+      <c r="A96" s="7"/>
+      <c r="D96" s="7"/>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97"/>
-      <c r="D97"/>
+      <c r="A97" s="7"/>
+      <c r="D97" s="7"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="A98"/>
-      <c r="D98"/>
+      <c r="A98" s="7"/>
+      <c r="D98" s="7"/>
     </row>
     <row r="99" ht="14.25">
-      <c r="A99"/>
-      <c r="D99"/>
+      <c r="A99" s="7"/>
+      <c r="D99" s="7"/>
     </row>
     <row r="100" ht="14.25">
-      <c r="A100"/>
-      <c r="D100"/>
+      <c r="A100" s="7"/>
+      <c r="D100" s="7"/>
     </row>
     <row r="101" ht="14.25">
-      <c r="A101"/>
-      <c r="D101"/>
+      <c r="A101" s="7"/>
+      <c r="D101" s="7"/>
     </row>
     <row r="102" ht="14.25">
-      <c r="A102"/>
-      <c r="D102"/>
+      <c r="A102" s="7"/>
+      <c r="D102" s="7"/>
     </row>
     <row r="103" ht="14.25">
-      <c r="A103"/>
-      <c r="D103"/>
+      <c r="A103" s="7"/>
+      <c r="D103" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -3197,7 +3200,7 @@
     <mergeCell ref="D100:D103"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
@@ -3214,906 +3217,906 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="8">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="11" t="s">
+      <c r="C2" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="11"/>
+      <c r="C3" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="11"/>
+      <c r="C4" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="10"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="11"/>
+      <c r="C5" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="11"/>
+      <c r="C7" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="11"/>
+      <c r="C8" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="11"/>
+      <c r="C9" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="10"/>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="8">
+      <c r="A10" s="9">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="C10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="11"/>
+      <c r="C11" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="10"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="11"/>
+      <c r="C12" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="11"/>
+      <c r="C13" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="10"/>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="8">
+      <c r="A14" s="9">
         <v>4</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D14" s="11" t="s">
+      <c r="C14" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="11"/>
+      <c r="C15" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="10"/>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="11"/>
+      <c r="C16" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D17" s="11"/>
+      <c r="C17" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="8">
+      <c r="A18" s="9">
         <v>5</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D18" s="11" t="s">
+      <c r="C18" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D19" s="11"/>
+      <c r="C19" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D20" s="11"/>
+      <c r="C20" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9" t="s">
+      <c r="A21" s="9"/>
+      <c r="B21" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="11"/>
+      <c r="C21" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="8">
+      <c r="A22" s="9">
         <v>6</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" s="11" t="s">
+      <c r="C22" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9" t="s">
+      <c r="A23" s="9"/>
+      <c r="B23" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D23" s="11"/>
+      <c r="C23" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9" t="s">
+      <c r="A24" s="9"/>
+      <c r="B24" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="11"/>
+      <c r="C24" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="10"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="11"/>
+      <c r="C25" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="10"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="8">
+      <c r="A26" s="9">
         <v>7</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="11" t="s">
+      <c r="C26" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9" t="s">
+      <c r="A27" s="9"/>
+      <c r="B27" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" s="11"/>
+      <c r="C27" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="9"/>
+      <c r="B28" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="11"/>
+      <c r="C28" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="10"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9" t="s">
+      <c r="A29" s="9"/>
+      <c r="B29" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="11"/>
+      <c r="C29" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="10"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="8">
+      <c r="A30" s="9">
         <v>8</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="11" t="s">
+      <c r="C30" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="11"/>
+      <c r="C31" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="10"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9" t="s">
+      <c r="A32" s="9"/>
+      <c r="B32" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" s="11"/>
+      <c r="C32" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="10"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9" t="s">
+      <c r="A33" s="9"/>
+      <c r="B33" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="11"/>
+      <c r="C33" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33" s="10"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="8">
+      <c r="A34" s="9">
         <v>9</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="11" t="s">
+      <c r="C34" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9" t="s">
+      <c r="A35" s="9"/>
+      <c r="B35" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" s="11"/>
+      <c r="C35" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="9"/>
+      <c r="B36" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" s="11"/>
+      <c r="C36" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="10"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="9"/>
+      <c r="B37" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" s="11"/>
+      <c r="C37" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" s="10"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="8">
+      <c r="A38" s="9">
         <v>10</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" s="11" t="s">
+      <c r="C38" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9" t="s">
+      <c r="A39" s="9"/>
+      <c r="B39" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="11"/>
+      <c r="C39" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="10"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9" t="s">
+      <c r="A40" s="9"/>
+      <c r="B40" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="11"/>
+      <c r="C40" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="10"/>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D41" s="11"/>
+      <c r="C41" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" s="10"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="8">
+      <c r="A42" s="9">
         <v>11</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="11" t="s">
+      <c r="C42" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9" t="s">
+      <c r="A43" s="9"/>
+      <c r="B43" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D43" s="11"/>
+      <c r="C43" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="10"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9" t="s">
+      <c r="A44" s="9"/>
+      <c r="B44" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="11"/>
+      <c r="C44" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="10"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9" t="s">
+      <c r="A45" s="9"/>
+      <c r="B45" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="11"/>
+      <c r="C45" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" s="10"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="8">
+      <c r="A46" s="9">
         <v>12</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="11" t="s">
+      <c r="C46" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9" t="s">
+      <c r="A47" s="9"/>
+      <c r="B47" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="11"/>
+      <c r="C47" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="10"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="11"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="10"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="11"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="10"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="8">
+      <c r="A50" s="9">
         <v>13</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50" s="11" t="s">
+      <c r="C50" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" s="10" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9" t="s">
+      <c r="A51" s="9"/>
+      <c r="B51" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D51" s="11"/>
+      <c r="C51" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" s="10"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9" t="s">
+      <c r="A52" s="9"/>
+      <c r="B52" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D52" s="11"/>
+      <c r="C52" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="10"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9" t="s">
+      <c r="A53" s="9"/>
+      <c r="B53" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53" s="11"/>
+      <c r="C53" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="10"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="8">
+      <c r="A54" s="9">
         <v>14</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" s="11" t="s">
+      <c r="C54" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9" t="s">
+      <c r="A55" s="9"/>
+      <c r="B55" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D55" s="11"/>
+      <c r="C55" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" s="10"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9" t="s">
+      <c r="A56" s="9"/>
+      <c r="B56" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" s="11"/>
+      <c r="C56" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D56" s="10"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="11"/>
+      <c r="A57" s="9"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="10"/>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="8">
+      <c r="A58" s="9">
         <v>15</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D58" s="11" t="s">
+      <c r="C58" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9" t="s">
+      <c r="A59" s="9"/>
+      <c r="B59" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="11"/>
+      <c r="C59" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" s="10"/>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9" t="s">
+      <c r="A60" s="9"/>
+      <c r="B60" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="11"/>
+      <c r="C60" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" s="10"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9" t="s">
+      <c r="A61" s="9"/>
+      <c r="B61" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D61" s="11"/>
+      <c r="C61" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D61" s="10"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="11"/>
+      <c r="A62" s="9"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="10"/>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="11"/>
+      <c r="A63" s="9"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="10"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="11"/>
+      <c r="A64" s="9"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="10"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="11"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="10"/>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="11"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="10"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="11"/>
+      <c r="A67" s="9"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="10"/>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="11"/>
+      <c r="A68" s="9"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="10"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="11"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="10"/>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="11"/>
+      <c r="A70" s="9"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="10"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="11"/>
+      <c r="A71" s="9"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="10"/>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="11"/>
+      <c r="A72" s="9"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="10"/>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="11"/>
+      <c r="A73" s="9"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="10"/>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="11"/>
+      <c r="A74" s="9"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="10"/>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="11"/>
+      <c r="A75" s="9"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="10"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="11"/>
+      <c r="A76" s="9"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="10"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="11"/>
+      <c r="A77" s="9"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="10"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="11"/>
+      <c r="A78" s="9"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="10"/>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="11"/>
+      <c r="A79" s="9"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="10"/>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
+      <c r="A80" s="9"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="10"/>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="11"/>
+      <c r="A81" s="9"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="10"/>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="11"/>
+      <c r="A82" s="9"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="10"/>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="11"/>
+      <c r="A83" s="9"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="10"/>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="8"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="11"/>
+      <c r="A84" s="9"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="10"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85" s="8"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="11"/>
+      <c r="A85" s="9"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="10"/>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="11"/>
+      <c r="A86" s="9"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="10"/>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87" s="8"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="11"/>
+      <c r="A87" s="9"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="10"/>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88" s="8"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="11"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="10"/>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89" s="8"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="11"/>
+      <c r="A89" s="9"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="10"/>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90" s="8"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="11"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="10"/>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91" s="8"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="11"/>
+      <c r="A91" s="9"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="10"/>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92" s="8"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="11"/>
+      <c r="A92" s="9"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="10"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="A93" s="8"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="10"/>
-      <c r="D93" s="11"/>
+      <c r="A93" s="9"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="10"/>
     </row>
     <row r="94" ht="14.25">
-      <c r="A94" s="8"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="11"/>
+      <c r="A94" s="9"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="10"/>
     </row>
     <row r="95" ht="14.25">
-      <c r="A95" s="8"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="11"/>
+      <c r="A95" s="9"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="10"/>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96" s="8"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
+      <c r="A96" s="9"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="10"/>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97" s="8"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="11"/>
+      <c r="A97" s="9"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="10"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="A98" s="8"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="11"/>
+      <c r="A98" s="9"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="10"/>
     </row>
     <row r="99" ht="14.25">
-      <c r="A99" s="8"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="11"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="10"/>
     </row>
     <row r="100" ht="14.25">
-      <c r="A100" s="8"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="11"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="10"/>
     </row>
     <row r="101" ht="14.25">
-      <c r="A101" s="8"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="11"/>
+      <c r="A101" s="9"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="50">

--- a/ADET/teams and titles of adet.xlsx
+++ b/ADET/teams and titles of adet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="3g" sheetId="1" state="visible" r:id="rId2"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="242">
   <si>
     <t>group</t>
   </si>
@@ -30,6 +30,9 @@
     <t>tittle</t>
   </si>
   <si>
+    <t>grades</t>
+  </si>
+  <si>
     <t xml:space="preserve">andrei onate</t>
   </si>
   <si>
@@ -219,6 +222,15 @@
     <t>pallago</t>
   </si>
   <si>
+    <t>ferrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sari sari store inventory management system</t>
+  </si>
+  <si>
+    <t>lubbui</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -342,6 +354,39 @@
     <t>duarte</t>
   </si>
   <si>
+    <t>pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">track and claim</t>
+  </si>
+  <si>
+    <t>calcidona</t>
+  </si>
+  <si>
+    <t>minette</t>
+  </si>
+  <si>
+    <t>jarabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bright smile</t>
+  </si>
+  <si>
+    <t>medrano</t>
+  </si>
+  <si>
+    <t>galera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">student complaint tracking system</t>
+  </si>
+  <si>
+    <t>resoco</t>
+  </si>
+  <si>
+    <t>molina</t>
+  </si>
+  <si>
     <t>title</t>
   </si>
   <si>
@@ -372,9 +417,6 @@
     <t>yutoc</t>
   </si>
   <si>
-    <t>lubbui</t>
-  </si>
-  <si>
     <t>sayno</t>
   </si>
   <si>
@@ -409,9 +451,6 @@
   </si>
   <si>
     <t>lucanas</t>
-  </si>
-  <si>
-    <t>molina</t>
   </si>
   <si>
     <t>daludung</t>
@@ -755,7 +794,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -768,6 +807,12 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1305,29 +1350,32 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="4"/>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="4"/>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -1336,23 +1384,23 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -1361,23 +1409,23 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="4"/>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="4"/>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -1386,23 +1434,23 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="4"/>
       <c r="B12" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="4"/>
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -1411,23 +1459,23 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="4"/>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="4"/>
       <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3"/>
     </row>
@@ -1436,23 +1484,26 @@
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="4"/>
       <c r="B18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3"/>
+      <c r="D18">
+        <v>89</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="4"/>
       <c r="B19" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3"/>
     </row>
@@ -1461,23 +1512,23 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="4"/>
       <c r="B21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="4"/>
       <c r="B22" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3"/>
     </row>
@@ -1486,23 +1537,23 @@
         <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="4"/>
       <c r="B24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="4"/>
       <c r="B25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" s="3"/>
     </row>
@@ -1511,23 +1562,23 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="4"/>
       <c r="B27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" s="4"/>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="3"/>
     </row>
@@ -1536,23 +1587,23 @@
         <v>10</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="4"/>
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" s="3"/>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="4"/>
       <c r="B31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" s="3"/>
     </row>
@@ -1561,18 +1612,21 @@
         <v>11</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="5"/>
       <c r="B33" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C33" s="4"/>
+      <c r="D33">
+        <v>91</v>
+      </c>
     </row>
     <row r="34" ht="14.25">
       <c r="A34" s="5"/>
@@ -1583,16 +1637,16 @@
         <v>12</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="5"/>
       <c r="B36" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="4"/>
     </row>
@@ -1605,23 +1659,23 @@
         <v>13</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="5"/>
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C39" s="4"/>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="5"/>
       <c r="B40" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" s="4"/>
     </row>
@@ -1630,23 +1684,23 @@
         <v>14</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="5"/>
       <c r="B42" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="5"/>
       <c r="B43" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C43" s="3"/>
     </row>
@@ -1655,18 +1709,21 @@
         <v>15</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" ht="14.25">
       <c r="A45" s="5"/>
       <c r="B45" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C45" s="4"/>
+      <c r="D45">
+        <v>90</v>
+      </c>
     </row>
     <row r="46" ht="14.25">
       <c r="A46" s="5"/>
@@ -1677,23 +1734,26 @@
         <v>16</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" ht="14.25">
       <c r="A48" s="5"/>
       <c r="B48" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C48" s="3"/>
+      <c r="D48">
+        <v>89</v>
+      </c>
     </row>
     <row r="49" ht="14.25">
       <c r="A49" s="5"/>
       <c r="B49" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C49" s="3"/>
     </row>
@@ -1702,16 +1762,16 @@
         <v>17</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" ht="14.25">
       <c r="A51" s="5"/>
       <c r="B51" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C51" s="3"/>
     </row>
@@ -1719,8 +1779,28 @@
       <c r="A52" s="5"/>
       <c r="C52" s="3"/>
     </row>
+    <row r="53" ht="14.25">
+      <c r="B53" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="B54" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="C55" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="35">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="A5:A7"/>
@@ -1755,6 +1835,7 @@
     <mergeCell ref="C47:C49"/>
     <mergeCell ref="A50:A52"/>
     <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C53:C55"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1774,16 +1855,16 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="14.25">
@@ -1791,32 +1872,35 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="4"/>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D3" s="4"/>
+      <c r="E3">
+        <v>90</v>
+      </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="4"/>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D4" s="4"/>
     </row>
@@ -1825,32 +1909,35 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="4"/>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D6" s="4"/>
+      <c r="E6">
+        <v>90</v>
+      </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="4"/>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D7" s="4"/>
     </row>
@@ -1859,32 +1946,32 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="4"/>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D9" s="4"/>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="4"/>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D10" s="4"/>
     </row>
@@ -1893,32 +1980,32 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="4"/>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3"/>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="4"/>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D13" s="3"/>
     </row>
@@ -1927,32 +2014,32 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="4"/>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D15" s="4"/>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="4"/>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D16" s="4"/>
     </row>
@@ -1961,32 +2048,32 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="4"/>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="4"/>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D19" s="4"/>
     </row>
@@ -1995,32 +2082,35 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="4"/>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D21" s="5"/>
+      <c r="E21">
+        <v>91</v>
+      </c>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="4"/>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D22" s="5"/>
     </row>
@@ -2029,32 +2119,32 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="5"/>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D24" s="4"/>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="5"/>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D25" s="4"/>
     </row>
@@ -2063,66 +2153,133 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="5"/>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D27" s="5"/>
+      <c r="E27">
+        <v>93</v>
+      </c>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" s="5"/>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D28" s="5"/>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="B29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="5"/>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>74</v>
+      </c>
       <c r="D30" s="5"/>
+      <c r="E30">
+        <v>90</v>
+      </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="5"/>
+      <c r="B31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
       <c r="D31" s="5"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32"/>
-      <c r="D32"/>
+      <c r="A32" s="5"/>
+      <c r="B32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="5">
+        <v>92</v>
+      </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33"/>
-      <c r="D33"/>
+      <c r="A33" s="5"/>
+      <c r="B33" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
     </row>
     <row r="34" ht="14.25">
       <c r="A34"/>
-      <c r="D34"/>
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="35" ht="14.25">
       <c r="A35"/>
-      <c r="D35"/>
+      <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" ht="14.25">
       <c r="A36"/>
-      <c r="D36"/>
+      <c r="B36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="5"/>
     </row>
     <row r="37" ht="14.25">
       <c r="A37"/>
@@ -2385,7 +2542,7 @@
       <c r="D101"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="A5:A7"/>
@@ -2406,6 +2563,10 @@
     <mergeCell ref="D26:D28"/>
     <mergeCell ref="A29:A31"/>
     <mergeCell ref="D29:D31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="D34:D36"/>
     <mergeCell ref="A98:A101"/>
     <mergeCell ref="D98:D101"/>
   </mergeCells>
@@ -2420,729 +2581,732 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="9.140625"/>
-    <col customWidth="1" min="2" max="2" style="7" width="22.7109375"/>
-    <col customWidth="1" min="3" max="3" style="8" width="8.8515625"/>
-    <col customWidth="1" min="4" max="4" style="9" width="63.28125"/>
+    <col min="1" max="1" style="8" width="9.140625"/>
+    <col customWidth="1" min="2" max="2" style="9" width="22.7109375"/>
+    <col customWidth="1" min="3" max="3" style="10" width="8.8515625"/>
+    <col customWidth="1" min="4" max="4" style="11" width="63.28125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>107</v>
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>110</v>
+      <c r="B2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="10"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="12"/>
     </row>
     <row r="4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="12"/>
     </row>
     <row r="5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="10"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="9">
+      <c r="A6" s="11">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>115</v>
+      <c r="B6" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="10"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="12"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="12"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="9">
+      <c r="A9" s="11">
         <v>3</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>119</v>
+      <c r="B9" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="10"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="11">
+        <v>4</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="11">
+        <v>5</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="11"/>
+      <c r="B17" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="11"/>
+      <c r="B18" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="9">
-        <v>4</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="9">
-        <v>5</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="12"/>
+      <c r="C18" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="14"/>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="12"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="9">
+      <c r="A20" s="11">
         <v>6</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>133</v>
+      <c r="B20" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="9"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="9"/>
-      <c r="D23" s="9"/>
+      <c r="A23" s="11"/>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="9">
+      <c r="A24" s="11">
         <v>7</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>138</v>
+      <c r="B24" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="12"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="14"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="12"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="14"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="9"/>
-      <c r="B27" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="12"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="14"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="9">
+      <c r="A28" s="11">
         <v>8</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>143</v>
+      <c r="B28" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="9"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="11"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="9"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="11"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="9"/>
-      <c r="B31" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="9"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="11"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="9">
+      <c r="A32" s="11">
         <v>9</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>148</v>
+      <c r="B32" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" s="9"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="11"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" s="9"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="11"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="9"/>
-      <c r="B35" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" s="9"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="11"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="9">
+      <c r="A36" s="11">
         <v>10</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>153</v>
+      <c r="B36" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" s="10"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="12"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="9"/>
-      <c r="B38" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38" s="10"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="12"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="9"/>
-      <c r="D39" s="10"/>
+      <c r="A39" s="11"/>
+      <c r="D39" s="12"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="9">
+      <c r="A40" s="11">
         <v>11</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>157</v>
+      <c r="B40" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="9"/>
-      <c r="B41" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" s="9"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="11"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="9"/>
-      <c r="B42" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42" s="9"/>
+      <c r="A42" s="11"/>
+      <c r="B42" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" s="11"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="9"/>
-      <c r="B43" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43" s="9"/>
+      <c r="A43" s="11"/>
+      <c r="B43" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="11"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D44" s="7"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D44" s="9"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D45" s="7"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D45" s="9"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D46" s="7"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" s="9"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D47" s="7"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D47" s="9"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="7"/>
-      <c r="D48" s="7"/>
+      <c r="A48" s="9"/>
+      <c r="D48" s="9"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="7"/>
-      <c r="D49" s="7"/>
+      <c r="A49" s="9"/>
+      <c r="D49" s="9"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="7"/>
-      <c r="D50" s="7"/>
+      <c r="A50" s="9"/>
+      <c r="D50" s="9"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="7"/>
-      <c r="D51" s="7"/>
+      <c r="A51" s="9"/>
+      <c r="D51" s="9"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="A52" s="9"/>
+      <c r="D52" s="9"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="7"/>
-      <c r="D53" s="7"/>
+      <c r="A53" s="9"/>
+      <c r="D53" s="9"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="7"/>
-      <c r="D54" s="7"/>
+      <c r="A54" s="9"/>
+      <c r="D54" s="9"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="7"/>
-      <c r="D55" s="7"/>
+      <c r="A55" s="9"/>
+      <c r="D55" s="9"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="7"/>
-      <c r="D56" s="7"/>
+      <c r="A56" s="9"/>
+      <c r="D56" s="9"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="7"/>
-      <c r="D57" s="7"/>
+      <c r="A57" s="9"/>
+      <c r="D57" s="9"/>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="7"/>
-      <c r="D58" s="7"/>
+      <c r="A58" s="9"/>
+      <c r="D58" s="9"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="7"/>
-      <c r="D59" s="7"/>
+      <c r="A59" s="9"/>
+      <c r="D59" s="9"/>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="7"/>
-      <c r="D60" s="7"/>
+      <c r="A60" s="9"/>
+      <c r="D60" s="9"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="7"/>
-      <c r="D61" s="7"/>
+      <c r="A61" s="9"/>
+      <c r="D61" s="9"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="7"/>
-      <c r="D62" s="7"/>
+      <c r="A62" s="9"/>
+      <c r="D62" s="9"/>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="7"/>
-      <c r="D63" s="7"/>
+      <c r="A63" s="9"/>
+      <c r="D63" s="9"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="7"/>
-      <c r="D64" s="7"/>
+      <c r="A64" s="9"/>
+      <c r="D64" s="9"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="7"/>
-      <c r="D65" s="7"/>
+      <c r="A65" s="9"/>
+      <c r="D65" s="9"/>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="7"/>
-      <c r="D66" s="7"/>
+      <c r="A66" s="9"/>
+      <c r="D66" s="9"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="7"/>
-      <c r="D67" s="7"/>
+      <c r="A67" s="9"/>
+      <c r="D67" s="9"/>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="7"/>
-      <c r="D68" s="7"/>
+      <c r="A68" s="9"/>
+      <c r="D68" s="9"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="7"/>
-      <c r="D69" s="7"/>
+      <c r="A69" s="9"/>
+      <c r="D69" s="9"/>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="7"/>
-      <c r="D70" s="7"/>
+      <c r="A70" s="9"/>
+      <c r="D70" s="9"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="7"/>
-      <c r="D71" s="7"/>
+      <c r="A71" s="9"/>
+      <c r="D71" s="9"/>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="7"/>
-      <c r="D72" s="7"/>
+      <c r="A72" s="9"/>
+      <c r="D72" s="9"/>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="7"/>
-      <c r="D73" s="7"/>
+      <c r="A73" s="9"/>
+      <c r="D73" s="9"/>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="7"/>
-      <c r="D74" s="7"/>
+      <c r="A74" s="9"/>
+      <c r="D74" s="9"/>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="7"/>
-      <c r="D75" s="7"/>
+      <c r="A75" s="9"/>
+      <c r="D75" s="9"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="7"/>
-      <c r="D76" s="7"/>
+      <c r="A76" s="9"/>
+      <c r="D76" s="9"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="7"/>
-      <c r="D77" s="7"/>
+      <c r="A77" s="9"/>
+      <c r="D77" s="9"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="7"/>
-      <c r="D78" s="7"/>
+      <c r="A78" s="9"/>
+      <c r="D78" s="9"/>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="7"/>
-      <c r="D79" s="7"/>
+      <c r="A79" s="9"/>
+      <c r="D79" s="9"/>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="7"/>
-      <c r="D80" s="7"/>
+      <c r="A80" s="9"/>
+      <c r="D80" s="9"/>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="7"/>
-      <c r="D81" s="7"/>
+      <c r="A81" s="9"/>
+      <c r="D81" s="9"/>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="7"/>
-      <c r="D82" s="7"/>
+      <c r="A82" s="9"/>
+      <c r="D82" s="9"/>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="7"/>
-      <c r="D83" s="7"/>
+      <c r="A83" s="9"/>
+      <c r="D83" s="9"/>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="7"/>
-      <c r="D84" s="7"/>
+      <c r="A84" s="9"/>
+      <c r="D84" s="9"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85" s="7"/>
-      <c r="D85" s="7"/>
+      <c r="A85" s="9"/>
+      <c r="D85" s="9"/>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86" s="7"/>
-      <c r="D86" s="7"/>
+      <c r="A86" s="9"/>
+      <c r="D86" s="9"/>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87" s="7"/>
-      <c r="D87" s="7"/>
+      <c r="A87" s="9"/>
+      <c r="D87" s="9"/>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88" s="7"/>
-      <c r="D88" s="7"/>
+      <c r="A88" s="9"/>
+      <c r="D88" s="9"/>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89" s="7"/>
-      <c r="D89" s="7"/>
+      <c r="A89" s="9"/>
+      <c r="D89" s="9"/>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90" s="7"/>
-      <c r="D90" s="7"/>
+      <c r="A90" s="9"/>
+      <c r="D90" s="9"/>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91" s="7"/>
-      <c r="D91" s="7"/>
+      <c r="A91" s="9"/>
+      <c r="D91" s="9"/>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92" s="7"/>
-      <c r="D92" s="7"/>
+      <c r="A92" s="9"/>
+      <c r="D92" s="9"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="A93" s="7"/>
-      <c r="D93" s="7"/>
+      <c r="A93" s="9"/>
+      <c r="D93" s="9"/>
     </row>
     <row r="94" ht="14.25">
-      <c r="A94" s="7"/>
-      <c r="D94" s="7"/>
+      <c r="A94" s="9"/>
+      <c r="D94" s="9"/>
     </row>
     <row r="95" ht="14.25">
-      <c r="A95" s="7"/>
-      <c r="D95" s="7"/>
+      <c r="A95" s="9"/>
+      <c r="D95" s="9"/>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96" s="7"/>
-      <c r="D96" s="7"/>
+      <c r="A96" s="9"/>
+      <c r="D96" s="9"/>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97" s="7"/>
-      <c r="D97" s="7"/>
+      <c r="A97" s="9"/>
+      <c r="D97" s="9"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="A98" s="7"/>
-      <c r="D98" s="7"/>
+      <c r="A98" s="9"/>
+      <c r="D98" s="9"/>
     </row>
     <row r="99" ht="14.25">
-      <c r="A99" s="7"/>
-      <c r="D99" s="7"/>
+      <c r="A99" s="9"/>
+      <c r="D99" s="9"/>
     </row>
     <row r="100" ht="14.25">
-      <c r="A100" s="7"/>
-      <c r="D100" s="7"/>
+      <c r="A100" s="9"/>
+      <c r="D100" s="9"/>
     </row>
     <row r="101" ht="14.25">
-      <c r="A101" s="7"/>
-      <c r="D101" s="7"/>
+      <c r="A101" s="9"/>
+      <c r="D101" s="9"/>
     </row>
     <row r="102" ht="14.25">
-      <c r="A102" s="7"/>
-      <c r="D102" s="7"/>
+      <c r="A102" s="9"/>
+      <c r="D102" s="9"/>
     </row>
     <row r="103" ht="14.25">
-      <c r="A103" s="7"/>
-      <c r="D103" s="7"/>
+      <c r="A103" s="9"/>
+      <c r="D103" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -3217,911 +3381,930 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>107</v>
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="9">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>165</v>
+      <c r="B2" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2">
+        <v>82</v>
+      </c>
+      <c r="F2" s="5">
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="10"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3">
+        <v>82</v>
+      </c>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4">
+        <v>82</v>
+      </c>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="10"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5">
+        <v>82</v>
+      </c>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="9">
+      <c r="A6" s="11">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>170</v>
+      <c r="B6" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="10"/>
+      <c r="A7" s="11"/>
+      <c r="B7" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="12"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="10"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" s="12"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="11"/>
+      <c r="B9" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="11">
+        <v>3</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="12"/>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="11">
+        <v>4</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="11"/>
+      <c r="B16" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="11"/>
+      <c r="B17" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="11">
+        <v>5</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="12"/>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="11"/>
+      <c r="B20" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="12"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="11">
+        <v>6</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="12"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="11">
+        <v>7</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="11"/>
+      <c r="B27" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="12"/>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="11"/>
+      <c r="B28" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="12"/>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="11">
+        <v>8</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="12"/>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="12"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="12"/>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="11">
+        <v>9</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="12"/>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D36" s="12"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="11"/>
+      <c r="B37" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D37" s="12"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="11">
+        <v>10</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="12"/>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="11"/>
+      <c r="B40" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="11"/>
+      <c r="B41" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="12"/>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" s="11">
+        <v>11</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" s="11"/>
+      <c r="B43" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="12"/>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" s="11"/>
+      <c r="B44" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" s="11"/>
+      <c r="B45" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" s="11">
+        <v>12</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" s="11"/>
+      <c r="B47" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="12"/>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" s="11"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="12"/>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" s="11"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="12"/>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" s="11">
+        <v>13</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="11"/>
+      <c r="B51" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" s="12"/>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="11"/>
+      <c r="B52" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" s="12"/>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="11"/>
+      <c r="B53" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" s="12"/>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="A54" s="11">
+        <v>14</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55" s="11"/>
+      <c r="B55" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D55" s="12"/>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56" s="11"/>
+      <c r="B56" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D56" s="12"/>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="11"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="12"/>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="11">
+        <v>15</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="9">
-        <v>3</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C58" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59" s="11"/>
+      <c r="B59" s="9" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="7" t="s">
+      <c r="C59" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D59" s="12"/>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="11"/>
+      <c r="B60" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="7" t="s">
+      <c r="C60" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D60" s="12"/>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="11"/>
+      <c r="B61" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="10"/>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="9">
-        <v>4</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="A18" s="9">
-        <v>5</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D20" s="10"/>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="9">
-        <v>6</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="10"/>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="10"/>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" s="9">
-        <v>7</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="A27" s="9"/>
-      <c r="B27" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" s="10"/>
-    </row>
-    <row r="28" ht="14.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="10"/>
-    </row>
-    <row r="29" ht="14.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="10"/>
-    </row>
-    <row r="30" ht="14.25">
-      <c r="A30" s="9">
-        <v>8</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25">
-      <c r="A31" s="9"/>
-      <c r="B31" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="10"/>
-    </row>
-    <row r="32" ht="14.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" s="10"/>
-    </row>
-    <row r="33" ht="14.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="10"/>
-    </row>
-    <row r="34" ht="14.25">
-      <c r="A34" s="9">
-        <v>9</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25">
-      <c r="A35" s="9"/>
-      <c r="B35" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" s="10"/>
-    </row>
-    <row r="36" ht="14.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" s="10"/>
-    </row>
-    <row r="37" ht="14.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" s="10"/>
-    </row>
-    <row r="38" ht="14.25">
-      <c r="A38" s="9">
-        <v>10</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="10"/>
-    </row>
-    <row r="40" ht="14.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="10"/>
-    </row>
-    <row r="41" ht="14.25">
-      <c r="A41" s="9"/>
-      <c r="B41" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D41" s="10"/>
-    </row>
-    <row r="42" ht="14.25">
-      <c r="A42" s="9">
-        <v>11</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25">
-      <c r="A43" s="9"/>
-      <c r="B43" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D43" s="10"/>
-    </row>
-    <row r="44" ht="14.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D44" s="10"/>
-    </row>
-    <row r="45" ht="14.25">
-      <c r="A45" s="9"/>
-      <c r="B45" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="10"/>
-    </row>
-    <row r="46" ht="14.25">
-      <c r="A46" s="9">
-        <v>12</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25">
-      <c r="A47" s="9"/>
-      <c r="B47" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="10"/>
-    </row>
-    <row r="48" ht="14.25">
-      <c r="A48" s="9"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="10"/>
-    </row>
-    <row r="49" ht="14.25">
-      <c r="A49" s="9"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="10"/>
-    </row>
-    <row r="50" ht="14.25">
-      <c r="A50" s="9">
-        <v>13</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25">
-      <c r="A51" s="9"/>
-      <c r="B51" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D51" s="10"/>
-    </row>
-    <row r="52" ht="14.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D52" s="10"/>
-    </row>
-    <row r="53" ht="14.25">
-      <c r="A53" s="9"/>
-      <c r="B53" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53" s="10"/>
-    </row>
-    <row r="54" ht="14.25">
-      <c r="A54" s="9">
-        <v>14</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25">
-      <c r="A55" s="9"/>
-      <c r="B55" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D55" s="10"/>
-    </row>
-    <row r="56" ht="14.25">
-      <c r="A56" s="9"/>
-      <c r="B56" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" s="10"/>
-    </row>
-    <row r="57" ht="14.25">
-      <c r="A57" s="9"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="10"/>
-    </row>
-    <row r="58" ht="14.25">
-      <c r="A58" s="9">
-        <v>15</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25">
-      <c r="A59" s="9"/>
-      <c r="B59" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="10"/>
-    </row>
-    <row r="60" ht="14.25">
-      <c r="A60" s="9"/>
-      <c r="B60" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="10"/>
-    </row>
-    <row r="61" ht="14.25">
-      <c r="A61" s="9"/>
-      <c r="B61" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D61" s="10"/>
+      <c r="C61" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" s="12"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="9"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="10"/>
+      <c r="A62" s="11"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="12"/>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="9"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="10"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="12"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="9"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="10"/>
+      <c r="A64" s="11"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="12"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="9"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="10"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="12"/>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="9"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="10"/>
+      <c r="A66" s="11"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="12"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="9"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="10"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="12"/>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="9"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="10"/>
+      <c r="A68" s="11"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="12"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="9"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="10"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="12"/>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="9"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="10"/>
+      <c r="A70" s="11"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="12"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="9"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="10"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="12"/>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="9"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="10"/>
+      <c r="A72" s="11"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="12"/>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="9"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="10"/>
+      <c r="A73" s="11"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="12"/>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="9"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="10"/>
+      <c r="A74" s="11"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="12"/>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="9"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="10"/>
+      <c r="A75" s="11"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="12"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="9"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="10"/>
+      <c r="A76" s="11"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="12"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="9"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="10"/>
+      <c r="A77" s="11"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="12"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="9"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="10"/>
+      <c r="A78" s="11"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="12"/>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="9"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="10"/>
+      <c r="A79" s="11"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="12"/>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="9"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="10"/>
+      <c r="A80" s="11"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="12"/>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="9"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="10"/>
+      <c r="A81" s="11"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="12"/>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="9"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="10"/>
+      <c r="A82" s="11"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="12"/>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="9"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="10"/>
+      <c r="A83" s="11"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="12"/>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="9"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="10"/>
+      <c r="A84" s="11"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="12"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85" s="9"/>
-      <c r="B85" s="7"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="10"/>
+      <c r="A85" s="11"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="12"/>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86" s="9"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="10"/>
+      <c r="A86" s="11"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="12"/>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87" s="9"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="10"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="12"/>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88" s="9"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="10"/>
+      <c r="A88" s="11"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="12"/>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89" s="9"/>
-      <c r="B89" s="7"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="10"/>
+      <c r="A89" s="11"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="12"/>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90" s="9"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="10"/>
+      <c r="A90" s="11"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="12"/>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91" s="9"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="10"/>
+      <c r="A91" s="11"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="12"/>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92" s="9"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="10"/>
+      <c r="A92" s="11"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="12"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="A93" s="9"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="10"/>
+      <c r="A93" s="11"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="12"/>
     </row>
     <row r="94" ht="14.25">
-      <c r="A94" s="9"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="10"/>
+      <c r="A94" s="11"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="12"/>
     </row>
     <row r="95" ht="14.25">
-      <c r="A95" s="9"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="10"/>
+      <c r="A95" s="11"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="12"/>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96" s="9"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="10"/>
+      <c r="A96" s="11"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="12"/>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97" s="9"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="10"/>
+      <c r="A97" s="11"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="12"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="A98" s="9"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="10"/>
+      <c r="A98" s="11"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="12"/>
     </row>
     <row r="99" ht="14.25">
-      <c r="A99" s="9"/>
-      <c r="B99" s="7"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="10"/>
+      <c r="A99" s="11"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="12"/>
     </row>
     <row r="100" ht="14.25">
-      <c r="A100" s="9"/>
-      <c r="B100" s="7"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="10"/>
+      <c r="A100" s="11"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="12"/>
     </row>
     <row r="101" ht="14.25">
-      <c r="A101" s="9"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="10"/>
+      <c r="A101" s="11"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="51">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="D2:D5"/>
+    <mergeCell ref="F2:F5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="A10:A13"/>

--- a/ADET/teams and titles of adet.xlsx
+++ b/ADET/teams and titles of adet.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
   <si>
     <t>group</t>
   </si>
@@ -696,6 +696,9 @@
     <t>carino</t>
   </si>
   <si>
+    <t>yumul</t>
+  </si>
+  <si>
     <t>marcos</t>
   </si>
   <si>
@@ -738,10 +741,13 @@
     <t xml:space="preserve">research archiving system for bsit 3rd year</t>
   </si>
   <si>
-    <t>millamina</t>
+    <t xml:space="preserve">millamina / molina</t>
   </si>
   <si>
     <t>trisino</t>
+  </si>
+  <si>
+    <t>hidalgo</t>
   </si>
   <si>
     <t xml:space="preserve">barangay punta record management system</t>
@@ -794,7 +800,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -807,12 +813,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -836,6 +836,7 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1599,6 +1600,9 @@
         <v>42</v>
       </c>
       <c r="C30" s="3"/>
+      <c r="D30">
+        <v>89</v>
+      </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="4"/>
@@ -1649,6 +1653,9 @@
         <v>49</v>
       </c>
       <c r="C36" s="4"/>
+      <c r="D36">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="5"/>
@@ -1774,21 +1781,24 @@
         <v>66</v>
       </c>
       <c r="C51" s="3"/>
+      <c r="D51">
+        <v>91</v>
+      </c>
     </row>
     <row r="52" ht="14.25">
       <c r="A52" s="5"/>
       <c r="C52" s="3"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="54" ht="14.25">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C54" s="5"/>
@@ -2193,7 +2203,7 @@
       <c r="C29" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2228,7 +2238,7 @@
       <c r="C32" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="5" t="s">
         <v>116</v>
       </c>
       <c r="E32" s="5">
@@ -2254,7 +2264,7 @@
       <c r="C34" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="5" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2581,23 +2591,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="9.140625"/>
-    <col customWidth="1" min="2" max="2" style="9" width="22.7109375"/>
-    <col customWidth="1" min="3" max="3" style="10" width="8.8515625"/>
-    <col customWidth="1" min="4" max="4" style="11" width="63.28125"/>
+    <col min="1" max="1" style="6" width="9.140625"/>
+    <col customWidth="1" min="2" max="2" style="7" width="22.7109375"/>
+    <col customWidth="1" min="3" max="3" style="8" width="8.8515625"/>
+    <col customWidth="1" min="4" max="4" style="9" width="63.28125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>122</v>
       </c>
       <c r="E1" t="s">
@@ -2605,708 +2615,708 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="12"/>
+      <c r="C3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="10"/>
     </row>
     <row r="4">
-      <c r="A4" s="11"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="12"/>
+      <c r="C4" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="10"/>
     </row>
     <row r="5">
-      <c r="A5" s="11"/>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="12"/>
+      <c r="C5" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="11">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="12"/>
+      <c r="C7" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="12"/>
+      <c r="C8" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="11">
+      <c r="A9" s="9">
         <v>3</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" s="12"/>
+      <c r="C10" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="10"/>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" s="12"/>
+      <c r="C11" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="10"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="11">
+      <c r="A12" s="9">
         <v>4</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" s="11" t="s">
+      <c r="C12" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D13" s="11"/>
+      <c r="C13" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="9" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="11"/>
+      <c r="C14" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="9" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="11"/>
+      <c r="C15" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="9"/>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="11">
+      <c r="A16" s="9">
         <v>5</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" s="14" t="s">
+      <c r="C16" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="9" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="14"/>
+      <c r="C17" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="9"/>
+      <c r="B18" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="14"/>
+      <c r="C18" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="14"/>
+      <c r="C19" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="11">
+      <c r="A20" s="9">
         <v>6</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="11" t="s">
+      <c r="C20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="9" t="s">
+      <c r="A21" s="9"/>
+      <c r="B21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D21" s="11"/>
+      <c r="C21" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="9"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="9" t="s">
+      <c r="A22" s="9"/>
+      <c r="B22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D22" s="11"/>
+      <c r="C22" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="9"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="A23" s="9"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="11">
+      <c r="A24" s="9">
         <v>7</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D24" s="14" t="s">
+      <c r="C24" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="9" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" s="14"/>
+      <c r="C25" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="11"/>
-      <c r="B26" s="9" t="s">
+      <c r="A26" s="9"/>
+      <c r="B26" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="14"/>
+      <c r="C26" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="12"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="11"/>
-      <c r="B27" s="9" t="s">
+      <c r="A27" s="9"/>
+      <c r="B27" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" s="14"/>
+      <c r="C27" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="12"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="11">
+      <c r="A28" s="9">
         <v>8</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="11" t="s">
+      <c r="C28" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="9" t="s">
+      <c r="A29" s="9"/>
+      <c r="B29" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="11"/>
+      <c r="C29" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="9"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="9" t="s">
+      <c r="A30" s="9"/>
+      <c r="B30" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D30" s="11"/>
+      <c r="C30" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="9" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="11"/>
+      <c r="C31" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="9"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="11">
+      <c r="A32" s="9">
         <v>9</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="11" t="s">
+      <c r="C32" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="9" t="s">
+      <c r="A33" s="9"/>
+      <c r="B33" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="11"/>
+      <c r="C33" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="9"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="9"/>
+      <c r="B34" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" s="11"/>
+      <c r="C34" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="9"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="9" t="s">
+      <c r="A35" s="9"/>
+      <c r="B35" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="11"/>
+      <c r="C35" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="9"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="11">
+      <c r="A36" s="9">
         <v>10</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="C36" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="9"/>
+      <c r="B37" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D37" s="12"/>
+      <c r="C37" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="10"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="11"/>
-      <c r="B38" s="9" t="s">
+      <c r="A38" s="9"/>
+      <c r="B38" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D38" s="12"/>
+      <c r="C38" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="10"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="11"/>
-      <c r="D39" s="12"/>
+      <c r="A39" s="9"/>
+      <c r="D39" s="10"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="11">
+      <c r="A40" s="9">
         <v>11</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="11" t="s">
+      <c r="C40" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="11"/>
-      <c r="B41" s="9" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D41" s="11"/>
+      <c r="C41" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="9"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="11"/>
-      <c r="B42" s="9" t="s">
+      <c r="A42" s="9"/>
+      <c r="B42" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="11"/>
+      <c r="C42" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" s="9"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="11"/>
-      <c r="B43" s="9" t="s">
+      <c r="A43" s="9"/>
+      <c r="B43" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D43" s="11"/>
+      <c r="C43" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="9"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9" t="s">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D44" s="9"/>
+      <c r="D44" s="7"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9" t="s">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D45" s="9"/>
+      <c r="D45" s="7"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9" t="s">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D46" s="9"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9" t="s">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="D47" s="9"/>
+      <c r="D47" s="7"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="9"/>
-      <c r="D48" s="9"/>
+      <c r="A48" s="7"/>
+      <c r="D48" s="7"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="9"/>
-      <c r="D49" s="9"/>
+      <c r="A49" s="7"/>
+      <c r="D49" s="7"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="9"/>
-      <c r="D50" s="9"/>
+      <c r="A50" s="7"/>
+      <c r="D50" s="7"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="9"/>
-      <c r="D51" s="9"/>
+      <c r="A51" s="7"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="9"/>
-      <c r="D52" s="9"/>
+      <c r="A52" s="7"/>
+      <c r="D52" s="7"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="9"/>
-      <c r="D53" s="9"/>
+      <c r="A53" s="7"/>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="9"/>
-      <c r="D54" s="9"/>
+      <c r="A54" s="7"/>
+      <c r="D54" s="7"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="9"/>
-      <c r="D55" s="9"/>
+      <c r="A55" s="7"/>
+      <c r="D55" s="7"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="9"/>
-      <c r="D56" s="9"/>
+      <c r="A56" s="7"/>
+      <c r="D56" s="7"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="9"/>
-      <c r="D57" s="9"/>
+      <c r="A57" s="7"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="9"/>
-      <c r="D58" s="9"/>
+      <c r="A58" s="7"/>
+      <c r="D58" s="7"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="9"/>
-      <c r="D59" s="9"/>
+      <c r="A59" s="7"/>
+      <c r="D59" s="7"/>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="9"/>
-      <c r="D60" s="9"/>
+      <c r="A60" s="7"/>
+      <c r="D60" s="7"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="9"/>
-      <c r="D61" s="9"/>
+      <c r="A61" s="7"/>
+      <c r="D61" s="7"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="9"/>
-      <c r="D62" s="9"/>
+      <c r="A62" s="7"/>
+      <c r="D62" s="7"/>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="9"/>
-      <c r="D63" s="9"/>
+      <c r="A63" s="7"/>
+      <c r="D63" s="7"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="9"/>
-      <c r="D64" s="9"/>
+      <c r="A64" s="7"/>
+      <c r="D64" s="7"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="9"/>
-      <c r="D65" s="9"/>
+      <c r="A65" s="7"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="9"/>
-      <c r="D66" s="9"/>
+      <c r="A66" s="7"/>
+      <c r="D66" s="7"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="9"/>
-      <c r="D67" s="9"/>
+      <c r="A67" s="7"/>
+      <c r="D67" s="7"/>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="9"/>
-      <c r="D68" s="9"/>
+      <c r="A68" s="7"/>
+      <c r="D68" s="7"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="9"/>
-      <c r="D69" s="9"/>
+      <c r="A69" s="7"/>
+      <c r="D69" s="7"/>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="9"/>
-      <c r="D70" s="9"/>
+      <c r="A70" s="7"/>
+      <c r="D70" s="7"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="9"/>
-      <c r="D71" s="9"/>
+      <c r="A71" s="7"/>
+      <c r="D71" s="7"/>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="9"/>
-      <c r="D72" s="9"/>
+      <c r="A72" s="7"/>
+      <c r="D72" s="7"/>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="9"/>
-      <c r="D73" s="9"/>
+      <c r="A73" s="7"/>
+      <c r="D73" s="7"/>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="9"/>
-      <c r="D74" s="9"/>
+      <c r="A74" s="7"/>
+      <c r="D74" s="7"/>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="9"/>
-      <c r="D75" s="9"/>
+      <c r="A75" s="7"/>
+      <c r="D75" s="7"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="9"/>
-      <c r="D76" s="9"/>
+      <c r="A76" s="7"/>
+      <c r="D76" s="7"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="9"/>
-      <c r="D77" s="9"/>
+      <c r="A77" s="7"/>
+      <c r="D77" s="7"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="9"/>
-      <c r="D78" s="9"/>
+      <c r="A78" s="7"/>
+      <c r="D78" s="7"/>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="9"/>
-      <c r="D79" s="9"/>
+      <c r="A79" s="7"/>
+      <c r="D79" s="7"/>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="9"/>
-      <c r="D80" s="9"/>
+      <c r="A80" s="7"/>
+      <c r="D80" s="7"/>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="9"/>
-      <c r="D81" s="9"/>
+      <c r="A81" s="7"/>
+      <c r="D81" s="7"/>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="9"/>
-      <c r="D82" s="9"/>
+      <c r="A82" s="7"/>
+      <c r="D82" s="7"/>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="9"/>
-      <c r="D83" s="9"/>
+      <c r="A83" s="7"/>
+      <c r="D83" s="7"/>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="9"/>
-      <c r="D84" s="9"/>
+      <c r="A84" s="7"/>
+      <c r="D84" s="7"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85" s="9"/>
-      <c r="D85" s="9"/>
+      <c r="A85" s="7"/>
+      <c r="D85" s="7"/>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86" s="9"/>
-      <c r="D86" s="9"/>
+      <c r="A86" s="7"/>
+      <c r="D86" s="7"/>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87" s="9"/>
-      <c r="D87" s="9"/>
+      <c r="A87" s="7"/>
+      <c r="D87" s="7"/>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88" s="9"/>
-      <c r="D88" s="9"/>
+      <c r="A88" s="7"/>
+      <c r="D88" s="7"/>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89" s="9"/>
-      <c r="D89" s="9"/>
+      <c r="A89" s="7"/>
+      <c r="D89" s="7"/>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90" s="9"/>
-      <c r="D90" s="9"/>
+      <c r="A90" s="7"/>
+      <c r="D90" s="7"/>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91" s="9"/>
-      <c r="D91" s="9"/>
+      <c r="A91" s="7"/>
+      <c r="D91" s="7"/>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92" s="9"/>
-      <c r="D92" s="9"/>
+      <c r="A92" s="7"/>
+      <c r="D92" s="7"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="A93" s="9"/>
-      <c r="D93" s="9"/>
+      <c r="A93" s="7"/>
+      <c r="D93" s="7"/>
     </row>
     <row r="94" ht="14.25">
-      <c r="A94" s="9"/>
-      <c r="D94" s="9"/>
+      <c r="A94" s="7"/>
+      <c r="D94" s="7"/>
     </row>
     <row r="95" ht="14.25">
-      <c r="A95" s="9"/>
-      <c r="D95" s="9"/>
+      <c r="A95" s="7"/>
+      <c r="D95" s="7"/>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96" s="9"/>
-      <c r="D96" s="9"/>
+      <c r="A96" s="7"/>
+      <c r="D96" s="7"/>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97" s="9"/>
-      <c r="D97" s="9"/>
+      <c r="A97" s="7"/>
+      <c r="D97" s="7"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="A98" s="9"/>
-      <c r="D98" s="9"/>
+      <c r="A98" s="7"/>
+      <c r="D98" s="7"/>
     </row>
     <row r="99" ht="14.25">
-      <c r="A99" s="9"/>
-      <c r="D99" s="9"/>
+      <c r="A99" s="7"/>
+      <c r="D99" s="7"/>
     </row>
     <row r="100" ht="14.25">
-      <c r="A100" s="9"/>
-      <c r="D100" s="9"/>
+      <c r="A100" s="7"/>
+      <c r="D100" s="7"/>
     </row>
     <row r="101" ht="14.25">
-      <c r="A101" s="9"/>
-      <c r="D101" s="9"/>
+      <c r="A101" s="7"/>
+      <c r="D101" s="7"/>
     </row>
     <row r="102" ht="14.25">
-      <c r="A102" s="9"/>
-      <c r="D102" s="9"/>
+      <c r="A102" s="7"/>
+      <c r="D102" s="7"/>
     </row>
     <row r="103" ht="14.25">
-      <c r="A103" s="9"/>
-      <c r="D103" s="9"/>
+      <c r="A103" s="7"/>
+      <c r="D103" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -3381,30 +3391,30 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="11">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>178</v>
       </c>
       <c r="E2">
@@ -3415,890 +3425,978 @@
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="12"/>
+      <c r="C3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="10"/>
       <c r="E3">
         <v>82</v>
       </c>
       <c r="F3" s="5"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D4" s="12"/>
+      <c r="C4" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="10"/>
       <c r="E4">
         <v>82</v>
       </c>
       <c r="F4" s="5"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="12"/>
+      <c r="C5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="10"/>
       <c r="E5">
         <v>82</v>
       </c>
       <c r="F5" s="5"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="11">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="12"/>
+      <c r="C7" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" s="12"/>
+      <c r="C8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="12"/>
+      <c r="C9" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="10"/>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="11">
+      <c r="A10" s="9">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="C10" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>187</v>
       </c>
+      <c r="E10">
+        <v>92</v>
+      </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="9" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="12"/>
+      <c r="C11" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11">
+        <v>91</v>
+      </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="9" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="12"/>
+      <c r="C12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12">
+        <v>91</v>
+      </c>
+      <c r="F12">
+        <v>93</v>
+      </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" s="12"/>
+      <c r="C13" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13">
+        <v>91</v>
+      </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="11">
+      <c r="A14" s="9">
         <v>4</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>192</v>
       </c>
+      <c r="E14">
+        <v>94</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="9" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="12"/>
+      <c r="C15" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15">
+        <v>94</v>
+      </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="9" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="12"/>
+      <c r="C16" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16">
+        <v>94</v>
+      </c>
+      <c r="F16">
+        <v>94</v>
+      </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="9" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D17" s="12"/>
+      <c r="C17" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17">
+        <v>94</v>
+      </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="11">
+      <c r="A18" s="9">
         <v>5</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="C18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>197</v>
       </c>
+      <c r="E18">
+        <v>83</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="12"/>
+      <c r="C19" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19">
+        <v>83</v>
+      </c>
+      <c r="F19">
+        <v>85</v>
+      </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="11"/>
-      <c r="B20" s="9" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20" s="12"/>
+      <c r="C20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20">
+        <v>83</v>
+      </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="9" t="s">
+      <c r="A21" s="9"/>
+      <c r="B21" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="12"/>
+      <c r="C21" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21">
+        <v>86</v>
+      </c>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="11">
+      <c r="A22" s="9">
         <v>6</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="12" t="s">
+      <c r="C22" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="9" t="s">
+      <c r="A23" s="9"/>
+      <c r="B23" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="12"/>
+      <c r="C23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="9" t="s">
+      <c r="A24" s="9"/>
+      <c r="B24" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D24" s="12"/>
+      <c r="C24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="10"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="9" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D25" s="12"/>
+      <c r="C25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="10"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="11">
+      <c r="A26" s="9">
         <v>7</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D26" s="12" t="s">
+      <c r="C26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="11"/>
-      <c r="B27" s="9" t="s">
+      <c r="A27" s="9"/>
+      <c r="B27" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D27" s="12"/>
+      <c r="C27" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="11"/>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="9"/>
+      <c r="B28" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="12"/>
+      <c r="C28" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="10"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="9" t="s">
+      <c r="A29" s="9"/>
+      <c r="B29" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="12"/>
+      <c r="C29" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="10"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="11">
+      <c r="A30" s="9">
         <v>8</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="C30" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="9" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D31" s="12"/>
+      <c r="C31" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="10"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="9" t="s">
+      <c r="A32" s="9"/>
+      <c r="B32" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="12"/>
+      <c r="C32" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="10"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="9" t="s">
+      <c r="A33" s="9"/>
+      <c r="B33" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D33" s="12"/>
+      <c r="C33" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="10"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="11">
+      <c r="A34" s="9">
         <v>9</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D34" s="12" t="s">
+      <c r="C34" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="9" t="s">
+      <c r="A35" s="9"/>
+      <c r="B35" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D35" s="12"/>
+      <c r="C35" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="9"/>
+      <c r="B36" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D36" s="12"/>
+      <c r="C36" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D36" s="10"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="9"/>
+      <c r="B37" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D37" s="12"/>
+      <c r="C37" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D37" s="10"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="11">
+      <c r="A38" s="9">
         <v>10</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="12" t="s">
+      <c r="C38" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>222</v>
       </c>
+      <c r="E38">
+        <v>86</v>
+      </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="11"/>
-      <c r="B39" s="9" t="s">
+      <c r="A39" s="9"/>
+      <c r="B39" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D39" s="12"/>
+      <c r="C39" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="10"/>
+      <c r="E39">
+        <v>89</v>
+      </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="11"/>
-      <c r="B40" s="9" t="s">
+      <c r="A40" s="9"/>
+      <c r="B40" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D40" s="12"/>
+      <c r="C40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="10"/>
+      <c r="E40">
+        <v>85</v>
+      </c>
+      <c r="F40">
+        <v>91</v>
+      </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="11"/>
-      <c r="B41" s="9" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D41" s="12"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="10"/>
+      <c r="E41">
+        <v>88</v>
+      </c>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="11">
+      <c r="A42" s="9"/>
+      <c r="B42" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" s="10"/>
+      <c r="E42">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" s="9">
         <v>11</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D42" s="12" t="s">
+      <c r="B43" s="7" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="43" ht="14.25">
-      <c r="A43" s="11"/>
-      <c r="B43" s="9" t="s">
+      <c r="C43" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D43" s="12"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="11"/>
-      <c r="B44" s="9" t="s">
+      <c r="A44" s="9"/>
+      <c r="B44" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" s="12"/>
+      <c r="C44" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D44" s="10"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="11"/>
-      <c r="B45" s="9" t="s">
+      <c r="A45" s="9"/>
+      <c r="B45" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D45" s="12"/>
+      <c r="C45" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" s="10"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="11">
+      <c r="A46" s="9"/>
+      <c r="B46" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" s="10"/>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" s="9">
         <v>12</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D46" s="12" t="s">
+      <c r="B47" s="7" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="47" ht="14.25">
-      <c r="A47" s="11"/>
-      <c r="B47" s="9" t="s">
+      <c r="C47" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D47" s="12"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="11"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="12"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" s="10"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="11"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="12"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="10"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="11">
+      <c r="A50" s="9"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="10"/>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="9">
         <v>13</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D50" s="12" t="s">
+      <c r="B51" s="7" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="51" ht="14.25">
-      <c r="A51" s="11"/>
-      <c r="B51" s="9" t="s">
+      <c r="C51" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="9"/>
+      <c r="B52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D51" s="12"/>
-    </row>
-    <row r="52" ht="14.25">
-      <c r="A52" s="11"/>
-      <c r="B52" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D52" s="12"/>
+      <c r="C52" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" s="10"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="11"/>
-      <c r="B53" s="9" t="s">
+      <c r="A53" s="9"/>
+      <c r="B53" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" s="10"/>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="A54" s="9"/>
+      <c r="B54" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D53" s="12"/>
-    </row>
-    <row r="54" ht="14.25">
-      <c r="A54" s="11">
+      <c r="C54" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D54" s="10"/>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55" s="9">
         <v>14</v>
       </c>
-      <c r="B54" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D54" s="12" t="s">
+      <c r="B55" s="7" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="55" ht="14.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="9" t="s">
+      <c r="C55" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D55" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D55" s="12"/>
+      <c r="E55">
+        <v>90</v>
+      </c>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="11"/>
-      <c r="B56" s="9" t="s">
+      <c r="A56" s="9"/>
+      <c r="B56" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D56" s="12"/>
+      <c r="C56" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" s="10"/>
+      <c r="E56">
+        <v>80</v>
+      </c>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="11"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="12"/>
+      <c r="A57" s="9"/>
+      <c r="B57" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D57" s="10"/>
+      <c r="E57">
+        <v>88</v>
+      </c>
+      <c r="F57">
+        <v>90</v>
+      </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="11">
+      <c r="A58" s="9"/>
+      <c r="B58" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="6"/>
+      <c r="D58" s="10"/>
+      <c r="E58">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59" s="9">
         <v>15</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B59" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="9" t="s">
+      <c r="C59" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="9"/>
+      <c r="B60" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D59" s="12"/>
-    </row>
-    <row r="60" ht="14.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="9" t="s">
+      <c r="C60" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D60" s="10"/>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="9"/>
+      <c r="B61" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D60" s="12"/>
-    </row>
-    <row r="61" ht="14.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="9" t="s">
+      <c r="C61" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" s="10"/>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62" s="9"/>
+      <c r="B62" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" s="12"/>
-    </row>
-    <row r="62" ht="14.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="12"/>
+      <c r="C62" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D62" s="10"/>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="12"/>
+      <c r="A63" s="9"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="10"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="11"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="12"/>
+      <c r="A64" s="9"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="10"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="12"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="10"/>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="11"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="12"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="10"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="11"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="12"/>
+      <c r="A67" s="9"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="10"/>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="11"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="12"/>
+      <c r="A68" s="9"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="10"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="11"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="12"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="10"/>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="11"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="12"/>
+      <c r="A70" s="9"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="10"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="11"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="12"/>
+      <c r="A71" s="9"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="10"/>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="11"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="12"/>
+      <c r="A72" s="9"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="10"/>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="11"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="12"/>
+      <c r="A73" s="9"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="10"/>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="11"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="12"/>
+      <c r="A74" s="9"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="10"/>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="11"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="12"/>
+      <c r="A75" s="9"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="10"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="11"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="12"/>
+      <c r="A76" s="9"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="10"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="11"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="12"/>
+      <c r="A77" s="9"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="10"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="11"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="12"/>
+      <c r="A78" s="9"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="10"/>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="12"/>
+      <c r="A79" s="9"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="10"/>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="11"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="12"/>
+      <c r="A80" s="9"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="10"/>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="11"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="12"/>
+      <c r="A81" s="9"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="10"/>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="11"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="12"/>
+      <c r="A82" s="9"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="10"/>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="11"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="12"/>
+      <c r="A83" s="9"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="10"/>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="11"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="12"/>
+      <c r="A84" s="9"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="10"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85" s="11"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="12"/>
+      <c r="A85" s="9"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="10"/>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86" s="11"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="12"/>
+      <c r="A86" s="9"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="10"/>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87" s="11"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="12"/>
+      <c r="A87" s="9"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="10"/>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88" s="11"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="12"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="10"/>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89" s="11"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="12"/>
+      <c r="A89" s="9"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="10"/>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90" s="11"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="12"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="10"/>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91" s="11"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="12"/>
+      <c r="A91" s="9"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="10"/>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92" s="11"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="12"/>
+      <c r="A92" s="9"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="10"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="A93" s="11"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="12"/>
+      <c r="A93" s="9"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="10"/>
     </row>
     <row r="94" ht="14.25">
-      <c r="A94" s="11"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="12"/>
+      <c r="A94" s="9"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="10"/>
     </row>
     <row r="95" ht="14.25">
-      <c r="A95" s="11"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="12"/>
+      <c r="A95" s="9"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="10"/>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96" s="11"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="12"/>
+      <c r="A96" s="9"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="10"/>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97" s="11"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="12"/>
+      <c r="A97" s="9"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="10"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="A98" s="11"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="12"/>
+      <c r="A98" s="9"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="10"/>
     </row>
     <row r="99" ht="14.25">
-      <c r="A99" s="11"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="12"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="10"/>
     </row>
     <row r="100" ht="14.25">
-      <c r="A100" s="11"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="12"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="10"/>
     </row>
     <row r="101" ht="14.25">
-      <c r="A101" s="11"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="12"/>
+      <c r="A101" s="9"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="10"/>
+    </row>
+    <row r="102" ht="14.25">
+      <c r="A102" s="9"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="51">
@@ -4321,38 +4419,38 @@
     <mergeCell ref="D30:D33"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="D34:D37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="D38:D42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="D47:D50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="D51:D54"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="D55:D58"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="D59:D62"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="D75:D78"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="D79:D82"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="D83:D86"/>
+    <mergeCell ref="A87:A90"/>
+    <mergeCell ref="D87:D90"/>
+    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="D91:D94"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="D95:D98"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="D99:D102"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/ADET/teams and titles of adet.xlsx
+++ b/ADET/teams and titles of adet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\For-Teaching\ADET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5920B440-72E5-4B33-90B2-EB4E007D3751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED91FB7A-A01D-4FE7-B700-F6CFC976E9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,18 @@
     <sheet name="3e" sheetId="3" r:id="rId3"/>
     <sheet name="3d" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -892,10 +903,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -904,22 +921,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1168,13 +1179,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>5</v>
       </c>
       <c r="D2">
@@ -1182,11 +1193,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
+      <c r="A3" s="15"/>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="14"/>
+      <c r="C3" s="13"/>
       <c r="D3">
         <v>90</v>
       </c>
@@ -1195,23 +1206,23 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="13"/>
       <c r="D4">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="15">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
       <c r="D5">
@@ -1219,11 +1230,11 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="13"/>
       <c r="D6">
         <v>91</v>
       </c>
@@ -1232,51 +1243,60 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="14"/>
+      <c r="C7" s="13"/>
       <c r="D7">
         <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="15">
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>13</v>
       </c>
+      <c r="D8">
+        <v>92</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="13"/>
+      <c r="D9">
+        <v>89</v>
+      </c>
       <c r="E9">
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="14"/>
+      <c r="C10" s="13"/>
+      <c r="D10">
+        <v>89</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="A11" s="15">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D11">
@@ -1284,11 +1304,11 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="14"/>
+      <c r="C12" s="13"/>
       <c r="D12">
         <v>93</v>
       </c>
@@ -1297,79 +1317,88 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="14"/>
+      <c r="C13" s="13"/>
       <c r="D13">
         <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+      <c r="A14" s="15">
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>21</v>
       </c>
+      <c r="D14">
+        <v>93</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14"/>
+      <c r="C15" s="13"/>
+      <c r="D15">
+        <v>93</v>
+      </c>
       <c r="E15">
         <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14"/>
+      <c r="C16" s="13"/>
+      <c r="D16">
+        <v>93</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
+      <c r="A17" s="15">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="14"/>
+      <c r="C18" s="13"/>
       <c r="D18">
         <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="14"/>
+      <c r="C19" s="13"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+      <c r="A20" s="15">
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>29</v>
       </c>
       <c r="D20">
@@ -1377,11 +1406,11 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="14"/>
+      <c r="C21" s="13"/>
       <c r="D21">
         <v>91</v>
       </c>
@@ -1390,51 +1419,60 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="14"/>
+      <c r="C22" s="13"/>
       <c r="D22">
         <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="13">
+      <c r="A23" s="15">
         <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="13" t="s">
         <v>33</v>
       </c>
+      <c r="D23">
+        <v>90</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="14"/>
+      <c r="C24" s="13"/>
+      <c r="D24">
+        <v>90</v>
+      </c>
       <c r="E24">
         <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="14"/>
+      <c r="C25" s="13"/>
+      <c r="D25">
+        <v>90</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+      <c r="A26" s="15">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D26">
@@ -1442,11 +1480,11 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="14"/>
+      <c r="C27" s="13"/>
       <c r="D27">
         <v>89</v>
       </c>
@@ -1455,101 +1493,122 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="14"/>
+      <c r="C28" s="13"/>
       <c r="D28">
         <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="13">
+      <c r="A29" s="15">
         <v>10</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>41</v>
       </c>
+      <c r="D29">
+        <v>88</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="14"/>
+      <c r="C30" s="13"/>
       <c r="D30">
+        <v>88</v>
+      </c>
+      <c r="E30">
         <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="14"/>
+      <c r="C31" s="13"/>
+      <c r="D31">
+        <v>88</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
+      <c r="A32" s="14">
         <v>11</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="15" t="s">
         <v>45</v>
       </c>
+      <c r="D32">
+        <v>91</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
+      <c r="A33" s="14"/>
       <c r="B33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="13"/>
+      <c r="C33" s="15"/>
       <c r="D33">
         <v>91</v>
       </c>
+      <c r="E33">
+        <v>91</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="C34" s="13"/>
+      <c r="A34" s="14"/>
+      <c r="C34" s="15"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
+      <c r="A35" s="14">
         <v>12</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="15" t="s">
         <v>48</v>
       </c>
+      <c r="D35">
+        <v>89</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
+      <c r="A36" s="14"/>
       <c r="B36" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="13"/>
+      <c r="C36" s="15"/>
       <c r="D36">
+        <v>89</v>
+      </c>
+      <c r="E36">
         <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="C37" s="13"/>
+      <c r="A37" s="14"/>
+      <c r="C37" s="15"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
+      <c r="A38" s="14">
         <v>13</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D38">
@@ -1557,11 +1616,11 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
+      <c r="A39" s="14"/>
       <c r="B39" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="13"/>
+      <c r="C39" s="15"/>
       <c r="D39">
         <v>93</v>
       </c>
@@ -1570,126 +1629,150 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
+      <c r="A40" s="14"/>
       <c r="B40" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="13"/>
+      <c r="C40" s="15"/>
       <c r="D40">
         <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="12">
+      <c r="A41" s="14">
         <v>14</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>53</v>
       </c>
+      <c r="D41">
+        <v>90</v>
+      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
+      <c r="A42" s="14"/>
       <c r="B42" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="14"/>
+      <c r="C42" s="13"/>
+      <c r="D42">
+        <v>90</v>
+      </c>
       <c r="E42">
         <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
+      <c r="A43" s="14"/>
       <c r="B43" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="14"/>
+      <c r="C43" s="13"/>
+      <c r="D43">
+        <v>90</v>
+      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
+      <c r="A44" s="14">
         <v>15</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="15" t="s">
         <v>57</v>
       </c>
+      <c r="D44">
+        <v>89</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
+      <c r="A45" s="14"/>
       <c r="B45" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="13"/>
+      <c r="C45" s="15"/>
       <c r="D45">
+        <v>89</v>
+      </c>
+      <c r="E45">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
-      <c r="C46" s="13"/>
+      <c r="A46" s="14"/>
+      <c r="C46" s="15"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="12">
+      <c r="A47" s="14">
         <v>16</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="13" t="s">
         <v>60</v>
       </c>
+      <c r="D47">
+        <v>89</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+      <c r="A48" s="14"/>
       <c r="B48" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="14"/>
+      <c r="C48" s="13"/>
       <c r="D48">
         <v>89</v>
       </c>
+      <c r="E48">
+        <v>89</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+      <c r="A49" s="14"/>
       <c r="B49" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C49" s="14"/>
+      <c r="C49" s="13"/>
+      <c r="D49">
+        <v>89</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="12">
+      <c r="A50" s="14">
         <v>17</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="13" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+      <c r="A51" s="14"/>
       <c r="B51" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C51" s="14"/>
+      <c r="C51" s="13"/>
       <c r="D51">
         <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
-      <c r="C52" s="14"/>
+      <c r="A52" s="14"/>
+      <c r="C52" s="13"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="14" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1697,13 +1780,13 @@
       <c r="B54" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="12"/>
+      <c r="C54" s="14"/>
       <c r="D54">
         <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C55" s="12"/>
+      <c r="C55" s="14"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
@@ -1712,7 +1795,7 @@
       <c r="B56" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="13" t="s">
         <v>103</v>
       </c>
       <c r="D56">
@@ -1723,7 +1806,7 @@
       <c r="B57" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C57" s="14"/>
+      <c r="C57" s="13"/>
       <c r="D57">
         <v>93</v>
       </c>
@@ -1735,49 +1818,49 @@
       <c r="B58" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C58" s="14"/>
+      <c r="C58" s="13"/>
       <c r="D58">
         <v>93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="C44:C46"/>
     <mergeCell ref="C56:C58"/>
     <mergeCell ref="A47:A49"/>
     <mergeCell ref="C47:C49"/>
     <mergeCell ref="A50:A52"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="C53:C55"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="C8:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0"/>
@@ -1809,7 +1892,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -1818,35 +1901,35 @@
       <c r="C2" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="15" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
+      <c r="A3" s="15"/>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="15"/>
       <c r="E3">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
+      <c r="A4" s="15"/>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="13"/>
+      <c r="D4" s="15"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="15">
         <v>2</v>
       </c>
       <c r="B5" t="s">
@@ -1855,35 +1938,35 @@
       <c r="C5" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="15" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
+      <c r="A6" s="15"/>
       <c r="B6" t="s">
         <v>80</v>
       </c>
       <c r="C6" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="15"/>
       <c r="E6">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
+      <c r="A7" s="15"/>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="15"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="15">
         <v>3</v>
       </c>
       <c r="B8" t="s">
@@ -1892,7 +1975,7 @@
       <c r="C8" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="15" t="s">
         <v>83</v>
       </c>
       <c r="E8">
@@ -1900,27 +1983,27 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" t="s">
         <v>84</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="15"/>
       <c r="E9">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="15"/>
       <c r="B10" t="s">
         <v>85</v>
       </c>
       <c r="C10" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="13"/>
+      <c r="D10" s="15"/>
       <c r="E10">
         <v>90</v>
       </c>
@@ -1929,7 +2012,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="A11" s="15">
         <v>4</v>
       </c>
       <c r="B11" t="s">
@@ -1938,7 +2021,7 @@
       <c r="C11" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>87</v>
       </c>
       <c r="E11">
@@ -1946,14 +2029,14 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
+      <c r="A12" s="15"/>
       <c r="B12" t="s">
         <v>88</v>
       </c>
       <c r="C12" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="14"/>
+      <c r="D12" s="13"/>
       <c r="E12">
         <v>91</v>
       </c>
@@ -1962,20 +2045,20 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="15"/>
       <c r="B13" t="s">
         <v>89</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="14"/>
+      <c r="D13" s="13"/>
       <c r="E13">
         <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+      <c r="A14" s="15">
         <v>5</v>
       </c>
       <c r="B14" t="s">
@@ -1984,35 +2067,35 @@
       <c r="C14" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="15"/>
       <c r="B15" t="s">
         <v>92</v>
       </c>
       <c r="C15" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="13"/>
+      <c r="D15" s="15"/>
       <c r="F15">
         <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="15"/>
       <c r="B16" t="s">
         <v>93</v>
       </c>
       <c r="C16" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="13"/>
+      <c r="D16" s="15"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
+      <c r="A17" s="15">
         <v>6</v>
       </c>
       <c r="B17" t="s">
@@ -2021,35 +2104,35 @@
       <c r="C17" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="15"/>
       <c r="B18" t="s">
         <v>96</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="13"/>
+      <c r="D18" s="15"/>
       <c r="F18" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="15"/>
       <c r="B19" t="s">
         <v>97</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="13"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+      <c r="A20" s="15">
         <v>7</v>
       </c>
       <c r="B20" t="s">
@@ -2058,35 +2141,35 @@
       <c r="C20" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="14" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
+      <c r="A21" s="15"/>
       <c r="B21" t="s">
         <v>100</v>
       </c>
       <c r="C21" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="12"/>
+      <c r="D21" s="14"/>
       <c r="E21">
         <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
+      <c r="A22" s="15"/>
       <c r="B22" t="s">
         <v>101</v>
       </c>
       <c r="C22" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="12"/>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
+      <c r="A23" s="14">
         <v>8</v>
       </c>
       <c r="B23" t="s">
@@ -2095,7 +2178,7 @@
       <c r="C23" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="15" t="s">
         <v>103</v>
       </c>
       <c r="E23">
@@ -2103,14 +2186,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
+      <c r="A24" s="14"/>
       <c r="B24" t="s">
         <v>104</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="13"/>
+      <c r="D24" s="15"/>
       <c r="E24">
         <v>93</v>
       </c>
@@ -2119,20 +2202,20 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
+      <c r="A25" s="14"/>
       <c r="B25" t="s">
         <v>105</v>
       </c>
       <c r="C25" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="13"/>
+      <c r="D25" s="15"/>
       <c r="E25">
         <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
+      <c r="A26" s="14">
         <v>9</v>
       </c>
       <c r="B26" t="s">
@@ -2141,93 +2224,93 @@
       <c r="C26" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="14" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
+      <c r="A27" s="14"/>
       <c r="B27" t="s">
         <v>108</v>
       </c>
       <c r="C27" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="12"/>
+      <c r="D27" s="14"/>
       <c r="E27">
         <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
+      <c r="A28" s="14"/>
       <c r="B28" t="s">
         <v>109</v>
       </c>
       <c r="C28" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="12"/>
+      <c r="D28" s="14"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
+      <c r="A29" s="14"/>
       <c r="B29" t="s">
         <v>110</v>
       </c>
       <c r="C29" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="14" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
+      <c r="A30" s="14"/>
       <c r="B30" t="s">
         <v>112</v>
       </c>
       <c r="C30" t="s">
         <v>73</v>
       </c>
-      <c r="D30" s="12"/>
+      <c r="D30" s="14"/>
       <c r="E30">
         <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
+      <c r="A31" s="14"/>
       <c r="B31" t="s">
         <v>113</v>
       </c>
       <c r="C31" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="12"/>
+      <c r="D31" s="14"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
+      <c r="A32" s="14"/>
       <c r="B32" t="s">
         <v>114</v>
       </c>
       <c r="C32" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="14">
         <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
+      <c r="A33" s="14"/>
       <c r="B33" t="s">
         <v>116</v>
       </c>
       <c r="C33" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34"/>
@@ -2237,7 +2320,7 @@
       <c r="C34" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="14" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2249,7 +2332,7 @@
       <c r="C35" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="12"/>
+      <c r="D35" s="14"/>
       <c r="E35">
         <v>90</v>
       </c>
@@ -2262,7 +2345,7 @@
       <c r="C36" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="12"/>
+      <c r="D36" s="14"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37"/>
@@ -2509,23 +2592,42 @@
       <c r="D97"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="15"/>
-      <c r="D98" s="15"/>
+      <c r="A98" s="16"/>
+      <c r="D98" s="16"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
-      <c r="D99" s="15"/>
+      <c r="A99" s="16"/>
+      <c r="D99" s="16"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="15"/>
-      <c r="D100" s="15"/>
+      <c r="A100" s="16"/>
+      <c r="D100" s="16"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
-      <c r="D101" s="15"/>
+      <c r="A101" s="16"/>
+      <c r="D101" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="D26:D28"/>
     <mergeCell ref="D34:D36"/>
     <mergeCell ref="A98:A101"/>
     <mergeCell ref="D98:D101"/>
@@ -2533,25 +2635,6 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D8:D10"/>
   </mergeCells>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2587,7 +2670,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -2596,7 +2679,7 @@
       <c r="C2" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="19" t="s">
         <v>124</v>
       </c>
       <c r="E2">
@@ -2604,27 +2687,27 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="19"/>
       <c r="E3">
         <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="19"/>
       <c r="E4">
         <v>92</v>
       </c>
@@ -2633,20 +2716,20 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="6" t="s">
         <v>127</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="19"/>
       <c r="E5">
         <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -2655,7 +2738,7 @@
       <c r="C6" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="19" t="s">
         <v>129</v>
       </c>
       <c r="E6">
@@ -2663,14 +2746,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="6" t="s">
         <v>130</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="19"/>
       <c r="E7">
         <v>90</v>
       </c>
@@ -2679,20 +2762,20 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="19"/>
       <c r="E8">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="18">
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -2701,7 +2784,7 @@
       <c r="C9" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="19" t="s">
         <v>132</v>
       </c>
       <c r="E9">
@@ -2709,14 +2792,14 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="6" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="19"/>
       <c r="E10">
         <v>89</v>
       </c>
@@ -2725,20 +2808,20 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="6" t="s">
         <v>134</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="19"/>
       <c r="E11">
         <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="18">
         <v>4</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -2747,7 +2830,7 @@
       <c r="C12" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="18" t="s">
         <v>136</v>
       </c>
       <c r="E12">
@@ -2755,27 +2838,27 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="6" t="s">
         <v>137</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="18"/>
       <c r="E13">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="6" t="s">
         <v>138</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="10"/>
+      <c r="D14" s="18"/>
       <c r="E14">
         <v>89</v>
       </c>
@@ -2784,20 +2867,20 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="6" t="s">
         <v>139</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="18"/>
       <c r="E15">
         <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="18">
         <v>5</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -2806,7 +2889,7 @@
       <c r="C16" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="20" t="s">
         <v>141</v>
       </c>
       <c r="E16">
@@ -2814,27 +2897,27 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="6" t="s">
         <v>142</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="16"/>
+      <c r="D17" s="20"/>
       <c r="E17">
         <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="16"/>
+      <c r="D18" s="20"/>
       <c r="E18">
         <v>75</v>
       </c>
@@ -2843,20 +2926,20 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="6" t="s">
         <v>143</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="16"/>
+      <c r="D19" s="20"/>
       <c r="E19">
         <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="18">
         <v>6</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -2865,7 +2948,7 @@
       <c r="C20" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="18" t="s">
         <v>145</v>
       </c>
       <c r="E20">
@@ -2873,14 +2956,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="6" t="s">
         <v>146</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="10"/>
+      <c r="D21" s="18"/>
       <c r="E21">
         <v>90</v>
       </c>
@@ -2889,24 +2972,24 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="6" t="s">
         <v>147</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="10"/>
+      <c r="D22" s="18"/>
       <c r="E22">
         <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="D23" s="10"/>
+      <c r="A23" s="18"/>
+      <c r="D23" s="18"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="A24" s="18">
         <v>7</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -2915,7 +2998,7 @@
       <c r="C24" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="20" t="s">
         <v>150</v>
       </c>
       <c r="E24">
@@ -2923,27 +3006,27 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="6" t="s">
         <v>151</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="16"/>
+      <c r="D25" s="20"/>
       <c r="E25">
         <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="6" t="s">
         <v>152</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="16"/>
+      <c r="D26" s="20"/>
       <c r="E26">
         <v>92</v>
       </c>
@@ -2952,20 +3035,20 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="6" t="s">
         <v>153</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="16"/>
+      <c r="D27" s="20"/>
       <c r="E27">
         <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+      <c r="A28" s="18">
         <v>8</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -2974,7 +3057,7 @@
       <c r="C28" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="18" t="s">
         <v>155</v>
       </c>
       <c r="E28">
@@ -2982,27 +3065,27 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="6" t="s">
         <v>156</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="10"/>
+      <c r="D29" s="18"/>
       <c r="E29">
         <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="6" t="s">
         <v>157</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="10"/>
+      <c r="D30" s="18"/>
       <c r="E30">
         <v>88</v>
       </c>
@@ -3011,20 +3094,20 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="6" t="s">
         <v>158</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="10"/>
+      <c r="D31" s="18"/>
       <c r="E31">
         <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+      <c r="A32" s="18">
         <v>9</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -3033,7 +3116,7 @@
       <c r="C32" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="18" t="s">
         <v>160</v>
       </c>
       <c r="E32">
@@ -3041,27 +3124,27 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="6" t="s">
         <v>161</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="10"/>
+      <c r="D33" s="18"/>
       <c r="E33">
         <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="6" t="s">
         <v>162</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="10"/>
+      <c r="D34" s="18"/>
       <c r="E34">
         <v>88</v>
       </c>
@@ -3070,20 +3153,20 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
+      <c r="A35" s="18"/>
       <c r="B35" s="6" t="s">
         <v>163</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D35" s="10"/>
+      <c r="D35" s="18"/>
       <c r="E35">
         <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="10">
+      <c r="A36" s="18">
         <v>10</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -3092,7 +3175,7 @@
       <c r="C36" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="19" t="s">
         <v>165</v>
       </c>
       <c r="E36">
@@ -3100,14 +3183,14 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="6" t="s">
         <v>166</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="11"/>
+      <c r="D37" s="19"/>
       <c r="E37">
         <v>89</v>
       </c>
@@ -3116,24 +3199,24 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
+      <c r="A38" s="18"/>
       <c r="B38" s="6" t="s">
         <v>167</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D38" s="11"/>
+      <c r="D38" s="19"/>
       <c r="E38">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="D39" s="11"/>
+      <c r="A39" s="18"/>
+      <c r="D39" s="19"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="10">
+      <c r="A40" s="18">
         <v>11</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -3142,7 +3225,7 @@
       <c r="C40" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="18" t="s">
         <v>169</v>
       </c>
       <c r="E40">
@@ -3150,27 +3233,27 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
+      <c r="A41" s="18"/>
       <c r="B41" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="10"/>
+      <c r="D41" s="18"/>
       <c r="E41">
         <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
+      <c r="A42" s="18"/>
       <c r="B42" s="6" t="s">
         <v>170</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D42" s="10"/>
+      <c r="D42" s="18"/>
       <c r="E42">
         <v>90</v>
       </c>
@@ -3179,14 +3262,14 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="6" t="s">
         <v>171</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="10"/>
+      <c r="D43" s="18"/>
       <c r="E43">
         <v>89</v>
       </c>
@@ -3445,6 +3528,48 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="D32:D35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="D48:D51"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="D52:D55"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="D56:D59"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="D68:D71"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="D72:D75"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="D76:D79"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="D80:D83"/>
     <mergeCell ref="A96:A99"/>
     <mergeCell ref="D96:D99"/>
     <mergeCell ref="A100:A103"/>
@@ -3455,48 +3580,6 @@
     <mergeCell ref="D88:D91"/>
     <mergeCell ref="A92:A95"/>
     <mergeCell ref="D92:D95"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="D72:D75"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="D76:D79"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="D80:D83"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="D60:D63"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="D68:D71"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="D48:D51"/>
-    <mergeCell ref="A52:A55"/>
-    <mergeCell ref="D52:D55"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="D56:D59"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="D36:D39"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="D40:D43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="D32:D35"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="D9:D11"/>
   </mergeCells>
   <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3529,7 +3612,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -3538,60 +3621,60 @@
       <c r="C2" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="19" t="s">
         <v>177</v>
       </c>
       <c r="E2">
         <v>82</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="14">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="19"/>
       <c r="E3">
         <v>82</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="6" t="s">
         <v>179</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="19"/>
       <c r="E4">
         <v>82</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="14"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="6" t="s">
         <v>180</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="19"/>
       <c r="E5">
         <v>82</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -3600,7 +3683,7 @@
       <c r="C6" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="19" t="s">
         <v>182</v>
       </c>
       <c r="E6">
@@ -3608,14 +3691,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="6" t="s">
         <v>183</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="19"/>
       <c r="E7">
         <v>85</v>
       </c>
@@ -3624,33 +3707,33 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="6" t="s">
         <v>184</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="19"/>
       <c r="E8">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="6" t="s">
         <v>185</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="19"/>
       <c r="E9">
         <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="A10" s="18">
         <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -3659,7 +3742,7 @@
       <c r="C10" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="19" t="s">
         <v>186</v>
       </c>
       <c r="E10">
@@ -3667,27 +3750,27 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="6" t="s">
         <v>187</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="19"/>
       <c r="E11">
         <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="6" t="s">
         <v>188</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="19"/>
       <c r="E12">
         <v>91</v>
       </c>
@@ -3696,20 +3779,20 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="6" t="s">
         <v>189</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="19"/>
       <c r="E13">
         <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="18">
         <v>4</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -3718,7 +3801,7 @@
       <c r="C14" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="19" t="s">
         <v>191</v>
       </c>
       <c r="E14">
@@ -3726,27 +3809,27 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="6" t="s">
         <v>192</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="19"/>
       <c r="E15">
         <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="6" t="s">
         <v>193</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="19"/>
       <c r="E16">
         <v>94</v>
       </c>
@@ -3755,20 +3838,20 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="6" t="s">
         <v>194</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="19"/>
       <c r="E17">
         <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="18">
         <v>5</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -3777,7 +3860,7 @@
       <c r="C18" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="19" t="s">
         <v>196</v>
       </c>
       <c r="E18">
@@ -3785,14 +3868,14 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="6" t="s">
         <v>197</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="19"/>
       <c r="E19">
         <v>83</v>
       </c>
@@ -3801,33 +3884,33 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="6" t="s">
         <v>198</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="19"/>
       <c r="E20">
         <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="6" t="s">
         <v>199</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="19"/>
       <c r="E21">
         <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+      <c r="A22" s="18">
         <v>6</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3836,7 +3919,7 @@
       <c r="C22" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="19" t="s">
         <v>201</v>
       </c>
       <c r="E22">
@@ -3844,27 +3927,27 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="6" t="s">
         <v>202</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="19"/>
       <c r="E23">
         <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="6" t="s">
         <v>203</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="11"/>
+      <c r="D24" s="19"/>
       <c r="E24">
         <v>84</v>
       </c>
@@ -3873,20 +3956,20 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="6" t="s">
         <v>204</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="19"/>
       <c r="E25">
         <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
+      <c r="A26" s="18">
         <v>7</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -3895,7 +3978,7 @@
       <c r="C26" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="19" t="s">
         <v>206</v>
       </c>
       <c r="E26">
@@ -3903,14 +3986,14 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="6" t="s">
         <v>207</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D27" s="11"/>
+      <c r="D27" s="19"/>
       <c r="E27">
         <v>75</v>
       </c>
@@ -3919,33 +4002,33 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
+      <c r="A28" s="18"/>
       <c r="B28" s="6" t="s">
         <v>208</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D28" s="11"/>
+      <c r="D28" s="19"/>
       <c r="E28">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="6" t="s">
         <v>209</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="11"/>
+      <c r="D29" s="19"/>
       <c r="E29">
         <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+      <c r="A30" s="18">
         <v>8</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -3954,7 +4037,7 @@
       <c r="C30" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="19" t="s">
         <v>211</v>
       </c>
       <c r="E30">
@@ -3962,14 +4045,14 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="6" t="s">
         <v>212</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="11"/>
+      <c r="D31" s="19"/>
       <c r="E31">
         <v>90</v>
       </c>
@@ -3978,33 +4061,33 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="6" t="s">
         <v>213</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D32" s="11"/>
+      <c r="D32" s="19"/>
       <c r="E32">
         <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="6" t="s">
         <v>214</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D33" s="11"/>
+      <c r="D33" s="19"/>
       <c r="E33">
         <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="10">
+      <c r="A34" s="18">
         <v>9</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -4013,7 +4096,7 @@
       <c r="C34" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="19" t="s">
         <v>216</v>
       </c>
       <c r="E34">
@@ -4021,27 +4104,27 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
+      <c r="A35" s="18"/>
       <c r="B35" s="6" t="s">
         <v>217</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D35" s="11"/>
+      <c r="D35" s="19"/>
       <c r="E35">
         <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="6" t="s">
         <v>218</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D36" s="11"/>
+      <c r="D36" s="19"/>
       <c r="E36">
         <v>91</v>
       </c>
@@ -4050,20 +4133,20 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="6" t="s">
         <v>219</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D37" s="11"/>
+      <c r="D37" s="19"/>
       <c r="E37">
         <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="10">
+      <c r="A38" s="18">
         <v>10</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -4072,7 +4155,7 @@
       <c r="C38" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="19" t="s">
         <v>221</v>
       </c>
       <c r="E38">
@@ -4080,27 +4163,27 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
+      <c r="A39" s="18"/>
       <c r="B39" s="6" t="s">
         <v>222</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D39" s="11"/>
+      <c r="D39" s="19"/>
       <c r="E39">
         <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
+      <c r="A40" s="18"/>
       <c r="B40" s="6" t="s">
         <v>223</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="11"/>
+      <c r="D40" s="19"/>
       <c r="E40">
         <v>85</v>
       </c>
@@ -4109,31 +4192,31 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
+      <c r="A41" s="18"/>
       <c r="B41" s="6" t="s">
         <v>224</v>
       </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="11"/>
+      <c r="D41" s="19"/>
       <c r="E41">
         <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
+      <c r="A42" s="18"/>
       <c r="B42" s="6" t="s">
         <v>225</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D42" s="11"/>
+      <c r="D42" s="19"/>
       <c r="E42">
         <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="10">
+      <c r="A43" s="18">
         <v>11</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -4142,7 +4225,7 @@
       <c r="C43" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="19" t="s">
         <v>227</v>
       </c>
       <c r="E43">
@@ -4150,46 +4233,46 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="6" t="s">
         <v>228</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D44" s="11"/>
+      <c r="D44" s="19"/>
       <c r="E44">
         <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="6" t="s">
         <v>242</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D45" s="11"/>
+      <c r="D45" s="19"/>
       <c r="E45">
         <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="6" t="s">
         <v>229</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D46" s="11"/>
+      <c r="D46" s="19"/>
       <c r="E46">
         <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
+      <c r="A47" s="18">
         <v>12</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -4198,7 +4281,7 @@
       <c r="C47" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="19" t="s">
         <v>231</v>
       </c>
       <c r="E47">
@@ -4206,14 +4289,14 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="10"/>
+      <c r="A48" s="18"/>
       <c r="B48" s="6" t="s">
         <v>232</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D48" s="11"/>
+      <c r="D48" s="19"/>
       <c r="E48">
         <v>85</v>
       </c>
@@ -4222,19 +4305,19 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="10"/>
+      <c r="A49" s="18"/>
       <c r="B49" s="6"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="11"/>
+      <c r="D49" s="19"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="10"/>
+      <c r="A50" s="18"/>
       <c r="B50" s="6"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="11"/>
+      <c r="D50" s="19"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="10">
+      <c r="A51" s="18">
         <v>13</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -4243,7 +4326,7 @@
       <c r="C51" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="19" t="s">
         <v>234</v>
       </c>
       <c r="E51">
@@ -4251,27 +4334,27 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="10"/>
+      <c r="A52" s="18"/>
       <c r="B52" s="6" t="s">
         <v>98</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D52" s="11"/>
+      <c r="D52" s="19"/>
       <c r="E52">
         <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
+      <c r="A53" s="18"/>
       <c r="B53" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D53" s="11"/>
+      <c r="D53" s="19"/>
       <c r="E53">
         <v>88</v>
       </c>
@@ -4280,20 +4363,20 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="10"/>
+      <c r="A54" s="18"/>
       <c r="B54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D54" s="11"/>
+      <c r="D54" s="19"/>
       <c r="E54">
         <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="10">
+      <c r="A55" s="18">
         <v>14</v>
       </c>
       <c r="B55" s="6" t="s">
@@ -4302,7 +4385,7 @@
       <c r="C55" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="19" t="s">
         <v>237</v>
       </c>
       <c r="E55">
@@ -4310,27 +4393,27 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="10"/>
+      <c r="A56" s="18"/>
       <c r="B56" s="6" t="s">
         <v>238</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D56" s="11"/>
+      <c r="D56" s="19"/>
       <c r="E56">
         <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="10"/>
+      <c r="A57" s="18"/>
       <c r="B57" s="6" t="s">
         <v>239</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="11"/>
+      <c r="D57" s="19"/>
       <c r="E57">
         <v>88</v>
       </c>
@@ -4339,18 +4422,18 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="10"/>
+      <c r="A58" s="18"/>
       <c r="B58" s="6" t="s">
         <v>240</v>
       </c>
       <c r="C58" s="5"/>
-      <c r="D58" s="11"/>
+      <c r="D58" s="19"/>
       <c r="E58">
         <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="10">
+      <c r="A59" s="18">
         <v>15</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -4367,7 +4450,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="10"/>
+      <c r="A60" s="18"/>
       <c r="B60" s="6" t="s">
         <v>173</v>
       </c>
@@ -4380,7 +4463,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
+      <c r="A61" s="18"/>
       <c r="B61" s="6" t="s">
         <v>174</v>
       </c>
@@ -4393,7 +4476,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="10"/>
+      <c r="A62" s="18"/>
       <c r="B62" s="6" t="s">
         <v>175</v>
       </c>
@@ -4406,7 +4489,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
+      <c r="A63" s="10"/>
       <c r="B63" s="6" t="s">
         <v>247</v>
       </c>
@@ -4419,241 +4502,274 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="19"/>
+      <c r="A64" s="11"/>
       <c r="B64" s="6"/>
       <c r="C64" s="5"/>
       <c r="D64" s="7"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="19"/>
+      <c r="A65" s="11"/>
       <c r="B65" s="6"/>
       <c r="C65" s="5"/>
       <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="20"/>
+      <c r="A66" s="12"/>
       <c r="B66" s="6"/>
       <c r="C66" s="5"/>
       <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="10"/>
+      <c r="A67" s="18"/>
       <c r="B67" s="6"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="11"/>
+      <c r="D67" s="19"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="10"/>
+      <c r="A68" s="18"/>
       <c r="B68" s="6"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="11"/>
+      <c r="D68" s="19"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="10"/>
+      <c r="A69" s="18"/>
       <c r="B69" s="6"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="11"/>
+      <c r="D69" s="19"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="10"/>
+      <c r="A70" s="18"/>
       <c r="B70" s="6"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="11"/>
+      <c r="D70" s="19"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="10"/>
+      <c r="A71" s="18"/>
       <c r="B71" s="6"/>
       <c r="C71" s="5"/>
-      <c r="D71" s="11"/>
+      <c r="D71" s="19"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="10"/>
+      <c r="A72" s="18"/>
       <c r="B72" s="6"/>
       <c r="C72" s="5"/>
-      <c r="D72" s="11"/>
+      <c r="D72" s="19"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="10"/>
+      <c r="A73" s="18"/>
       <c r="B73" s="6"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="11"/>
+      <c r="D73" s="19"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="10"/>
+      <c r="A74" s="18"/>
       <c r="B74" s="6"/>
       <c r="C74" s="5"/>
-      <c r="D74" s="11"/>
+      <c r="D74" s="19"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="10"/>
+      <c r="A75" s="18"/>
       <c r="B75" s="6"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="11"/>
+      <c r="D75" s="19"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="10"/>
+      <c r="A76" s="18"/>
       <c r="B76" s="6"/>
       <c r="C76" s="5"/>
-      <c r="D76" s="11"/>
+      <c r="D76" s="19"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="10"/>
+      <c r="A77" s="18"/>
       <c r="B77" s="6"/>
       <c r="C77" s="5"/>
-      <c r="D77" s="11"/>
+      <c r="D77" s="19"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="10"/>
+      <c r="A78" s="18"/>
       <c r="B78" s="6"/>
       <c r="C78" s="5"/>
-      <c r="D78" s="11"/>
+      <c r="D78" s="19"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="10"/>
+      <c r="A79" s="18"/>
       <c r="B79" s="6"/>
       <c r="C79" s="5"/>
-      <c r="D79" s="11"/>
+      <c r="D79" s="19"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="10"/>
+      <c r="A80" s="18"/>
       <c r="B80" s="6"/>
       <c r="C80" s="5"/>
-      <c r="D80" s="11"/>
+      <c r="D80" s="19"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="10"/>
+      <c r="A81" s="18"/>
       <c r="B81" s="6"/>
       <c r="C81" s="5"/>
-      <c r="D81" s="11"/>
+      <c r="D81" s="19"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="10"/>
+      <c r="A82" s="18"/>
       <c r="B82" s="6"/>
       <c r="C82" s="5"/>
-      <c r="D82" s="11"/>
+      <c r="D82" s="19"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="10"/>
+      <c r="A83" s="18"/>
       <c r="B83" s="6"/>
       <c r="C83" s="5"/>
-      <c r="D83" s="11"/>
+      <c r="D83" s="19"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="10"/>
+      <c r="A84" s="18"/>
       <c r="B84" s="6"/>
       <c r="C84" s="5"/>
-      <c r="D84" s="11"/>
+      <c r="D84" s="19"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="10"/>
+      <c r="A85" s="18"/>
       <c r="B85" s="6"/>
       <c r="C85" s="5"/>
-      <c r="D85" s="11"/>
+      <c r="D85" s="19"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="10"/>
+      <c r="A86" s="18"/>
       <c r="B86" s="6"/>
       <c r="C86" s="5"/>
-      <c r="D86" s="11"/>
+      <c r="D86" s="19"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="10"/>
+      <c r="A87" s="18"/>
       <c r="B87" s="6"/>
       <c r="C87" s="5"/>
-      <c r="D87" s="11"/>
+      <c r="D87" s="19"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="10"/>
+      <c r="A88" s="18"/>
       <c r="B88" s="6"/>
       <c r="C88" s="5"/>
-      <c r="D88" s="11"/>
+      <c r="D88" s="19"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="10"/>
+      <c r="A89" s="18"/>
       <c r="B89" s="6"/>
       <c r="C89" s="5"/>
-      <c r="D89" s="11"/>
+      <c r="D89" s="19"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="10"/>
+      <c r="A90" s="18"/>
       <c r="B90" s="6"/>
       <c r="C90" s="5"/>
-      <c r="D90" s="11"/>
+      <c r="D90" s="19"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="10"/>
+      <c r="A91" s="18"/>
       <c r="B91" s="6"/>
       <c r="C91" s="5"/>
-      <c r="D91" s="11"/>
+      <c r="D91" s="19"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="10"/>
+      <c r="A92" s="18"/>
       <c r="B92" s="6"/>
       <c r="C92" s="5"/>
-      <c r="D92" s="11"/>
+      <c r="D92" s="19"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="10"/>
+      <c r="A93" s="18"/>
       <c r="B93" s="6"/>
       <c r="C93" s="5"/>
-      <c r="D93" s="11"/>
+      <c r="D93" s="19"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="10"/>
+      <c r="A94" s="18"/>
       <c r="B94" s="6"/>
       <c r="C94" s="5"/>
-      <c r="D94" s="11"/>
+      <c r="D94" s="19"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="10"/>
+      <c r="A95" s="18"/>
       <c r="B95" s="6"/>
       <c r="C95" s="5"/>
-      <c r="D95" s="11"/>
+      <c r="D95" s="19"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="10"/>
+      <c r="A96" s="18"/>
       <c r="B96" s="6"/>
       <c r="C96" s="5"/>
-      <c r="D96" s="11"/>
+      <c r="D96" s="19"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="10"/>
+      <c r="A97" s="18"/>
       <c r="B97" s="6"/>
       <c r="C97" s="5"/>
-      <c r="D97" s="11"/>
+      <c r="D97" s="19"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="10"/>
+      <c r="A98" s="18"/>
       <c r="B98" s="6"/>
       <c r="C98" s="5"/>
-      <c r="D98" s="11"/>
+      <c r="D98" s="19"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="10"/>
+      <c r="A99" s="18"/>
       <c r="B99" s="6"/>
       <c r="C99" s="5"/>
-      <c r="D99" s="11"/>
+      <c r="D99" s="19"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="10"/>
+      <c r="A100" s="18"/>
       <c r="B100" s="6"/>
       <c r="C100" s="5"/>
-      <c r="D100" s="11"/>
+      <c r="D100" s="19"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="10"/>
+      <c r="A101" s="18"/>
       <c r="B101" s="6"/>
       <c r="C101" s="5"/>
-      <c r="D101" s="11"/>
+      <c r="D101" s="19"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="10"/>
+      <c r="A102" s="18"/>
       <c r="B102" s="6"/>
       <c r="C102" s="5"/>
-      <c r="D102" s="11"/>
+      <c r="D102" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="D38:D42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="D79:D82"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="D47:D50"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="D51:D54"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="D55:D58"/>
     <mergeCell ref="A95:A98"/>
     <mergeCell ref="D95:D98"/>
     <mergeCell ref="A99:A102"/>
@@ -4670,39 +4786,6 @@
     <mergeCell ref="A75:A78"/>
     <mergeCell ref="D75:D78"/>
     <mergeCell ref="A79:A82"/>
-    <mergeCell ref="D79:D82"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="D47:D50"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="D51:D54"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="D55:D58"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="A38:A42"/>
-    <mergeCell ref="D38:D42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="D6:D9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1"/>
